--- a/docs/oc-mensuales/articulos-de-aseo-e-higiene/jun-2025.xlsx
+++ b/docs/oc-mensuales/articulos-de-aseo-e-higiene/jun-2025.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="OC jun-2025" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="OC jun-2025" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -549,7 +549,7 @@
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
@@ -610,7 +610,7 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de los Lagos </t>
+          <t>Los Lagos</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -671,7 +671,7 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Coquimbo </t>
+          <t>Coquimbo</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -793,7 +793,7 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>Región del Libertador General Bernardo O´Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
@@ -854,7 +854,7 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
@@ -915,7 +915,7 @@
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Valparaíso </t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
@@ -976,7 +976,7 @@
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Valparaíso </t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
@@ -1037,7 +1037,7 @@
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Maule </t>
+          <t>Maule</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
@@ -1098,7 +1098,7 @@
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de los Lagos </t>
+          <t>Los Lagos</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
@@ -1159,7 +1159,7 @@
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
@@ -1220,7 +1220,7 @@
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
@@ -1281,7 +1281,7 @@
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Maule </t>
+          <t>Maule</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
@@ -1342,7 +1342,7 @@
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Tarapacá  </t>
+          <t>Tarapacá</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
@@ -1464,7 +1464,7 @@
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de la Araucanía </t>
+          <t>Araucanía</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
@@ -1525,7 +1525,7 @@
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
@@ -1586,7 +1586,7 @@
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
@@ -1647,7 +1647,7 @@
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>Región del Ñuble</t>
+          <t>Ñuble</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
@@ -1708,7 +1708,7 @@
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Valparaíso </t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
@@ -1769,7 +1769,7 @@
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
@@ -1830,7 +1830,7 @@
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de la Araucanía </t>
+          <t>Araucanía</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
@@ -1891,7 +1891,7 @@
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Valparaíso </t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
@@ -1952,7 +1952,7 @@
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Valparaíso </t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
@@ -2013,7 +2013,7 @@
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
@@ -2074,7 +2074,7 @@
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
@@ -2135,7 +2135,7 @@
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Maule </t>
+          <t>Maule</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
@@ -2196,7 +2196,7 @@
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Antofagasta </t>
+          <t>Antofagasta</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
@@ -2257,7 +2257,7 @@
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
@@ -2318,7 +2318,7 @@
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I31" t="inlineStr">
@@ -2379,7 +2379,7 @@
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I32" t="inlineStr">
@@ -2440,7 +2440,7 @@
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I33" t="inlineStr">
@@ -2501,7 +2501,7 @@
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de la Araucanía </t>
+          <t>Araucanía</t>
         </is>
       </c>
       <c r="I34" t="inlineStr">
@@ -2562,7 +2562,7 @@
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de los Lagos </t>
+          <t>Los Lagos</t>
         </is>
       </c>
       <c r="I35" t="inlineStr">
@@ -2623,7 +2623,7 @@
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Antofagasta </t>
+          <t>Antofagasta</t>
         </is>
       </c>
       <c r="I36" t="inlineStr">
@@ -2684,7 +2684,7 @@
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Valparaíso </t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I37" t="inlineStr">
@@ -2745,7 +2745,7 @@
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I38" t="inlineStr">
@@ -2806,7 +2806,7 @@
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de los Lagos </t>
+          <t>Los Lagos</t>
         </is>
       </c>
       <c r="I39" t="inlineStr">
@@ -2867,7 +2867,7 @@
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I40" t="inlineStr">
@@ -2928,7 +2928,7 @@
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Coquimbo </t>
+          <t>Coquimbo</t>
         </is>
       </c>
       <c r="I41" t="inlineStr">
@@ -2989,7 +2989,7 @@
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de los Lagos </t>
+          <t>Los Lagos</t>
         </is>
       </c>
       <c r="I42" t="inlineStr">
@@ -3050,7 +3050,7 @@
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Coquimbo </t>
+          <t>Coquimbo</t>
         </is>
       </c>
       <c r="I43" t="inlineStr">
@@ -3111,7 +3111,7 @@
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Biobío </t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I44" t="inlineStr">
@@ -3172,7 +3172,7 @@
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I45" t="inlineStr">
@@ -3233,7 +3233,7 @@
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Coquimbo </t>
+          <t>Coquimbo</t>
         </is>
       </c>
       <c r="I46" t="inlineStr">
@@ -3294,7 +3294,7 @@
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Antofagasta </t>
+          <t>Antofagasta</t>
         </is>
       </c>
       <c r="I47" t="inlineStr">
@@ -3355,7 +3355,7 @@
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de los Lagos </t>
+          <t>Los Lagos</t>
         </is>
       </c>
       <c r="I48" t="inlineStr">
@@ -3416,7 +3416,7 @@
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Tarapacá  </t>
+          <t>Tarapacá</t>
         </is>
       </c>
       <c r="I49" t="inlineStr">
@@ -3477,7 +3477,7 @@
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Valparaíso </t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I50" t="inlineStr">
@@ -3538,7 +3538,7 @@
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I51" t="inlineStr">
@@ -3599,7 +3599,7 @@
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de la Araucanía </t>
+          <t>Araucanía</t>
         </is>
       </c>
       <c r="I52" t="inlineStr">
@@ -3660,7 +3660,7 @@
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Biobío </t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I53" t="inlineStr">
@@ -3721,7 +3721,7 @@
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I54" t="inlineStr">
@@ -3782,7 +3782,7 @@
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>Región de Arica y Parinacota</t>
+          <t>Arica y Parinacota</t>
         </is>
       </c>
       <c r="I55" t="inlineStr">
@@ -3843,7 +3843,7 @@
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Valparaíso </t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I56" t="inlineStr">
@@ -3904,7 +3904,7 @@
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I57" t="inlineStr">
@@ -3965,7 +3965,7 @@
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I58" t="inlineStr">
@@ -4026,7 +4026,7 @@
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Valparaíso </t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I59" t="inlineStr">
@@ -4148,7 +4148,7 @@
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>Región Aysén del General Carlos Ibáñez del Campo</t>
+          <t>Aysén</t>
         </is>
       </c>
       <c r="I61" t="inlineStr">
@@ -4209,7 +4209,7 @@
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I62" t="inlineStr">
@@ -4270,7 +4270,7 @@
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I63" t="inlineStr">
@@ -4331,7 +4331,7 @@
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>Región Aysén del General Carlos Ibáñez del Campo</t>
+          <t>Aysén</t>
         </is>
       </c>
       <c r="I64" t="inlineStr">
@@ -4453,7 +4453,7 @@
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>Región de Los Ríos</t>
+          <t>Los Ríos</t>
         </is>
       </c>
       <c r="I66" t="inlineStr">
@@ -4514,7 +4514,7 @@
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Maule </t>
+          <t>Maule</t>
         </is>
       </c>
       <c r="I67" t="inlineStr">
@@ -4575,7 +4575,7 @@
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>Región del Libertador General Bernardo O´Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I68" t="inlineStr">
@@ -4636,7 +4636,7 @@
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de los Lagos </t>
+          <t>Los Lagos</t>
         </is>
       </c>
       <c r="I69" t="inlineStr">
@@ -4697,7 +4697,7 @@
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I70" t="inlineStr">
@@ -4819,7 +4819,7 @@
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de la Araucanía </t>
+          <t>Araucanía</t>
         </is>
       </c>
       <c r="I72" t="inlineStr">
@@ -4880,7 +4880,7 @@
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I73" t="inlineStr">
@@ -4941,7 +4941,7 @@
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I74" t="inlineStr">
@@ -5002,7 +5002,7 @@
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>Región del Libertador General Bernardo O´Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I75" t="inlineStr">
@@ -5063,7 +5063,7 @@
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>Región de Los Ríos</t>
+          <t>Los Ríos</t>
         </is>
       </c>
       <c r="I76" t="inlineStr">
@@ -5124,7 +5124,7 @@
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Valparaíso </t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I77" t="inlineStr">
@@ -5185,7 +5185,7 @@
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I78" t="inlineStr">
@@ -5246,7 +5246,7 @@
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I79" t="inlineStr">
@@ -5307,7 +5307,7 @@
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de la Araucanía </t>
+          <t>Araucanía</t>
         </is>
       </c>
       <c r="I80" t="inlineStr">
@@ -5368,7 +5368,7 @@
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I81" t="inlineStr">
@@ -5551,7 +5551,7 @@
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Biobío </t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I84" t="inlineStr">
@@ -5612,7 +5612,7 @@
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I85" t="inlineStr">
@@ -5673,7 +5673,7 @@
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>Región de Los Ríos</t>
+          <t>Los Ríos</t>
         </is>
       </c>
       <c r="I86" t="inlineStr">
@@ -5734,7 +5734,7 @@
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>Región de Arica y Parinacota</t>
+          <t>Arica y Parinacota</t>
         </is>
       </c>
       <c r="I87" t="inlineStr">
@@ -5795,7 +5795,7 @@
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Biobío </t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I88" t="inlineStr">
@@ -5810,7 +5810,7 @@
       </c>
       <c r="K88" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Biobío </t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="L88" t="inlineStr">
@@ -5860,7 +5860,7 @@
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I89" t="inlineStr">
@@ -5921,7 +5921,7 @@
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>Región del Ñuble</t>
+          <t>Ñuble</t>
         </is>
       </c>
       <c r="I90" t="inlineStr">
@@ -5982,7 +5982,7 @@
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Biobío </t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I91" t="inlineStr">
@@ -6043,7 +6043,7 @@
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I92" t="inlineStr">
@@ -6104,7 +6104,7 @@
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I93" t="inlineStr">
@@ -6165,7 +6165,7 @@
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I94" t="inlineStr">
@@ -6226,7 +6226,7 @@
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de la Araucanía </t>
+          <t>Araucanía</t>
         </is>
       </c>
       <c r="I95" t="inlineStr">
@@ -6287,7 +6287,7 @@
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t>Región del Libertador General Bernardo O´Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I96" t="inlineStr">
@@ -6348,7 +6348,7 @@
       </c>
       <c r="H97" t="inlineStr">
         <is>
-          <t>Región de Arica y Parinacota</t>
+          <t>Arica y Parinacota</t>
         </is>
       </c>
       <c r="I97" t="inlineStr">
@@ -6409,7 +6409,7 @@
       </c>
       <c r="H98" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I98" t="inlineStr">
@@ -6470,7 +6470,7 @@
       </c>
       <c r="H99" t="inlineStr">
         <is>
-          <t>Región de Los Ríos</t>
+          <t>Los Ríos</t>
         </is>
       </c>
       <c r="I99" t="inlineStr">
@@ -6531,7 +6531,7 @@
       </c>
       <c r="H100" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I100" t="inlineStr">
@@ -6592,7 +6592,7 @@
       </c>
       <c r="H101" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I101" t="inlineStr">
@@ -6653,7 +6653,7 @@
       </c>
       <c r="H102" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de la Araucanía </t>
+          <t>Araucanía</t>
         </is>
       </c>
       <c r="I102" t="inlineStr">
@@ -6714,7 +6714,7 @@
       </c>
       <c r="H103" t="inlineStr">
         <is>
-          <t>Región de Arica y Parinacota</t>
+          <t>Arica y Parinacota</t>
         </is>
       </c>
       <c r="I103" t="inlineStr">
@@ -6775,7 +6775,7 @@
       </c>
       <c r="H104" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de la Araucanía </t>
+          <t>Araucanía</t>
         </is>
       </c>
       <c r="I104" t="inlineStr">
@@ -6836,7 +6836,7 @@
       </c>
       <c r="H105" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de la Araucanía </t>
+          <t>Araucanía</t>
         </is>
       </c>
       <c r="I105" t="inlineStr">
@@ -6897,7 +6897,7 @@
       </c>
       <c r="H106" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Antofagasta </t>
+          <t>Antofagasta</t>
         </is>
       </c>
       <c r="I106" t="inlineStr">
@@ -6958,7 +6958,7 @@
       </c>
       <c r="H107" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de los Lagos </t>
+          <t>Los Lagos</t>
         </is>
       </c>
       <c r="I107" t="inlineStr">
@@ -7019,7 +7019,7 @@
       </c>
       <c r="H108" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I108" t="inlineStr">
@@ -7080,7 +7080,7 @@
       </c>
       <c r="H109" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I109" t="inlineStr">
@@ -7141,7 +7141,7 @@
       </c>
       <c r="H110" t="inlineStr">
         <is>
-          <t>Región del Libertador General Bernardo O´Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I110" t="inlineStr">
@@ -7202,7 +7202,7 @@
       </c>
       <c r="H111" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I111" t="inlineStr">
@@ -7263,7 +7263,7 @@
       </c>
       <c r="H112" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de la Araucanía </t>
+          <t>Araucanía</t>
         </is>
       </c>
       <c r="I112" t="inlineStr">
@@ -7324,7 +7324,7 @@
       </c>
       <c r="H113" t="inlineStr">
         <is>
-          <t>Región Aysén del General Carlos Ibáñez del Campo</t>
+          <t>Aysén</t>
         </is>
       </c>
       <c r="I113" t="inlineStr">
@@ -7385,7 +7385,7 @@
       </c>
       <c r="H114" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Biobío </t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I114" t="inlineStr">
@@ -7446,7 +7446,7 @@
       </c>
       <c r="H115" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Biobío </t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I115" t="inlineStr">
@@ -7507,7 +7507,7 @@
       </c>
       <c r="H116" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de la Araucanía </t>
+          <t>Araucanía</t>
         </is>
       </c>
       <c r="I116" t="inlineStr">
@@ -7568,7 +7568,7 @@
       </c>
       <c r="H117" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Maule </t>
+          <t>Maule</t>
         </is>
       </c>
       <c r="I117" t="inlineStr">
@@ -7629,7 +7629,7 @@
       </c>
       <c r="H118" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Valparaíso </t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I118" t="inlineStr">
@@ -7690,7 +7690,7 @@
       </c>
       <c r="H119" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de los Lagos </t>
+          <t>Los Lagos</t>
         </is>
       </c>
       <c r="I119" t="inlineStr">
@@ -7751,7 +7751,7 @@
       </c>
       <c r="H120" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Valparaíso </t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I120" t="inlineStr">
@@ -7873,7 +7873,7 @@
       </c>
       <c r="H122" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I122" t="inlineStr">
@@ -7934,7 +7934,7 @@
       </c>
       <c r="H123" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de la Araucanía </t>
+          <t>Araucanía</t>
         </is>
       </c>
       <c r="I123" t="inlineStr">
@@ -7995,7 +7995,7 @@
       </c>
       <c r="H124" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I124" t="inlineStr">
@@ -8056,7 +8056,7 @@
       </c>
       <c r="H125" t="inlineStr">
         <is>
-          <t>Región de Los Ríos</t>
+          <t>Los Ríos</t>
         </is>
       </c>
       <c r="I125" t="inlineStr">
@@ -8117,7 +8117,7 @@
       </c>
       <c r="H126" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I126" t="inlineStr">
@@ -8178,7 +8178,7 @@
       </c>
       <c r="H127" t="inlineStr">
         <is>
-          <t>Región del Ñuble</t>
+          <t>Ñuble</t>
         </is>
       </c>
       <c r="I127" t="inlineStr">
@@ -8239,7 +8239,7 @@
       </c>
       <c r="H128" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I128" t="inlineStr">
@@ -8300,7 +8300,7 @@
       </c>
       <c r="H129" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de los Lagos </t>
+          <t>Los Lagos</t>
         </is>
       </c>
       <c r="I129" t="inlineStr">
@@ -8361,7 +8361,7 @@
       </c>
       <c r="H130" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Valparaíso </t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I130" t="inlineStr">
@@ -8422,7 +8422,7 @@
       </c>
       <c r="H131" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I131" t="inlineStr">
@@ -8483,7 +8483,7 @@
       </c>
       <c r="H132" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de la Araucanía </t>
+          <t>Araucanía</t>
         </is>
       </c>
       <c r="I132" t="inlineStr">
@@ -8544,7 +8544,7 @@
       </c>
       <c r="H133" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I133" t="inlineStr">
@@ -8605,7 +8605,7 @@
       </c>
       <c r="H134" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I134" t="inlineStr">
@@ -8666,7 +8666,7 @@
       </c>
       <c r="H135" t="inlineStr">
         <is>
-          <t>Región del Libertador General Bernardo O´Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I135" t="inlineStr">
@@ -8727,7 +8727,7 @@
       </c>
       <c r="H136" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de la Araucanía </t>
+          <t>Araucanía</t>
         </is>
       </c>
       <c r="I136" t="inlineStr">
@@ -8788,7 +8788,7 @@
       </c>
       <c r="H137" t="inlineStr">
         <is>
-          <t>Región del Libertador General Bernardo O´Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I137" t="inlineStr">
@@ -8910,7 +8910,7 @@
       </c>
       <c r="H139" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Maule </t>
+          <t>Maule</t>
         </is>
       </c>
       <c r="I139" t="inlineStr">
@@ -8971,7 +8971,7 @@
       </c>
       <c r="H140" t="inlineStr">
         <is>
-          <t>Región del Libertador General Bernardo O´Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I140" t="inlineStr">
@@ -9093,7 +9093,7 @@
       </c>
       <c r="H142" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Biobío </t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I142" t="inlineStr">
@@ -9154,7 +9154,7 @@
       </c>
       <c r="H143" t="inlineStr">
         <is>
-          <t>Región de Magallanes y de la Antártica</t>
+          <t>Magallanes</t>
         </is>
       </c>
       <c r="I143" t="inlineStr">
@@ -9215,7 +9215,7 @@
       </c>
       <c r="H144" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I144" t="inlineStr">
@@ -9276,7 +9276,7 @@
       </c>
       <c r="H145" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I145" t="inlineStr">
@@ -9337,7 +9337,7 @@
       </c>
       <c r="H146" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Valparaíso </t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I146" t="inlineStr">
@@ -9398,7 +9398,7 @@
       </c>
       <c r="H147" t="inlineStr">
         <is>
-          <t>Región de Magallanes y de la Antártica</t>
+          <t>Magallanes</t>
         </is>
       </c>
       <c r="I147" t="inlineStr">
@@ -9459,7 +9459,7 @@
       </c>
       <c r="H148" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I148" t="inlineStr">
@@ -9520,7 +9520,7 @@
       </c>
       <c r="H149" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de los Lagos </t>
+          <t>Los Lagos</t>
         </is>
       </c>
       <c r="I149" t="inlineStr">
@@ -9581,7 +9581,7 @@
       </c>
       <c r="H150" t="inlineStr">
         <is>
-          <t>Región de Los Ríos</t>
+          <t>Los Ríos</t>
         </is>
       </c>
       <c r="I150" t="inlineStr">
@@ -9642,7 +9642,7 @@
       </c>
       <c r="H151" t="inlineStr">
         <is>
-          <t>Región del Ñuble</t>
+          <t>Ñuble</t>
         </is>
       </c>
       <c r="I151" t="inlineStr">
@@ -9703,7 +9703,7 @@
       </c>
       <c r="H152" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de la Araucanía </t>
+          <t>Araucanía</t>
         </is>
       </c>
       <c r="I152" t="inlineStr">
@@ -9764,7 +9764,7 @@
       </c>
       <c r="H153" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de la Araucanía </t>
+          <t>Araucanía</t>
         </is>
       </c>
       <c r="I153" t="inlineStr">
@@ -9825,7 +9825,7 @@
       </c>
       <c r="H154" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I154" t="inlineStr">
@@ -9886,7 +9886,7 @@
       </c>
       <c r="H155" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I155" t="inlineStr">
@@ -9947,7 +9947,7 @@
       </c>
       <c r="H156" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de la Araucanía </t>
+          <t>Araucanía</t>
         </is>
       </c>
       <c r="I156" t="inlineStr">
@@ -10008,7 +10008,7 @@
       </c>
       <c r="H157" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Valparaíso </t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I157" t="inlineStr">
@@ -10069,7 +10069,7 @@
       </c>
       <c r="H158" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de la Araucanía </t>
+          <t>Araucanía</t>
         </is>
       </c>
       <c r="I158" t="inlineStr">
@@ -10130,7 +10130,7 @@
       </c>
       <c r="H159" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de la Araucanía </t>
+          <t>Araucanía</t>
         </is>
       </c>
       <c r="I159" t="inlineStr">
@@ -10191,7 +10191,7 @@
       </c>
       <c r="H160" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I160" t="inlineStr">
@@ -10252,7 +10252,7 @@
       </c>
       <c r="H161" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Valparaíso </t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I161" t="inlineStr">
@@ -10313,7 +10313,7 @@
       </c>
       <c r="H162" t="inlineStr">
         <is>
-          <t>Región del Ñuble</t>
+          <t>Ñuble</t>
         </is>
       </c>
       <c r="I162" t="inlineStr">
@@ -10374,7 +10374,7 @@
       </c>
       <c r="H163" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de la Araucanía </t>
+          <t>Araucanía</t>
         </is>
       </c>
       <c r="I163" t="inlineStr">
@@ -10435,7 +10435,7 @@
       </c>
       <c r="H164" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Maule </t>
+          <t>Maule</t>
         </is>
       </c>
       <c r="I164" t="inlineStr">
@@ -10496,7 +10496,7 @@
       </c>
       <c r="H165" t="inlineStr">
         <is>
-          <t>Región del Libertador General Bernardo O´Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I165" t="inlineStr">
@@ -10557,7 +10557,7 @@
       </c>
       <c r="H166" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I166" t="inlineStr">
@@ -10618,7 +10618,7 @@
       </c>
       <c r="H167" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I167" t="inlineStr">
@@ -10679,7 +10679,7 @@
       </c>
       <c r="H168" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I168" t="inlineStr">
@@ -10740,7 +10740,7 @@
       </c>
       <c r="H169" t="inlineStr">
         <is>
-          <t>Región del Ñuble</t>
+          <t>Ñuble</t>
         </is>
       </c>
       <c r="I169" t="inlineStr">
@@ -10801,7 +10801,7 @@
       </c>
       <c r="H170" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I170" t="inlineStr">
@@ -10862,7 +10862,7 @@
       </c>
       <c r="H171" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Biobío </t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I171" t="inlineStr">
@@ -10923,7 +10923,7 @@
       </c>
       <c r="H172" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I172" t="inlineStr">
@@ -10984,7 +10984,7 @@
       </c>
       <c r="H173" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Valparaíso </t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I173" t="inlineStr">
@@ -11045,7 +11045,7 @@
       </c>
       <c r="H174" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Valparaíso </t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I174" t="inlineStr">
@@ -11106,7 +11106,7 @@
       </c>
       <c r="H175" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I175" t="inlineStr">
@@ -11167,7 +11167,7 @@
       </c>
       <c r="H176" t="inlineStr">
         <is>
-          <t>Región de Arica y Parinacota</t>
+          <t>Arica y Parinacota</t>
         </is>
       </c>
       <c r="I176" t="inlineStr">
@@ -11228,7 +11228,7 @@
       </c>
       <c r="H177" t="inlineStr">
         <is>
-          <t>Región de Magallanes y de la Antártica</t>
+          <t>Magallanes</t>
         </is>
       </c>
       <c r="I177" t="inlineStr">
@@ -11289,7 +11289,7 @@
       </c>
       <c r="H178" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de la Araucanía </t>
+          <t>Araucanía</t>
         </is>
       </c>
       <c r="I178" t="inlineStr">
@@ -11350,7 +11350,7 @@
       </c>
       <c r="H179" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Coquimbo </t>
+          <t>Coquimbo</t>
         </is>
       </c>
       <c r="I179" t="inlineStr">
@@ -11411,7 +11411,7 @@
       </c>
       <c r="H180" t="inlineStr">
         <is>
-          <t>Región del Ñuble</t>
+          <t>Ñuble</t>
         </is>
       </c>
       <c r="I180" t="inlineStr">
@@ -11472,7 +11472,7 @@
       </c>
       <c r="H181" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Biobío </t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I181" t="inlineStr">
@@ -11533,7 +11533,7 @@
       </c>
       <c r="H182" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I182" t="inlineStr">
@@ -11594,7 +11594,7 @@
       </c>
       <c r="H183" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Valparaíso </t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I183" t="inlineStr">
@@ -11655,7 +11655,7 @@
       </c>
       <c r="H184" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I184" t="inlineStr">
@@ -11777,7 +11777,7 @@
       </c>
       <c r="H186" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de la Araucanía </t>
+          <t>Araucanía</t>
         </is>
       </c>
       <c r="I186" t="inlineStr">
@@ -11838,7 +11838,7 @@
       </c>
       <c r="H187" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Atacama </t>
+          <t>Atacama</t>
         </is>
       </c>
       <c r="I187" t="inlineStr">
@@ -11899,7 +11899,7 @@
       </c>
       <c r="H188" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I188" t="inlineStr">
@@ -11960,7 +11960,7 @@
       </c>
       <c r="H189" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Maule </t>
+          <t>Maule</t>
         </is>
       </c>
       <c r="I189" t="inlineStr">
@@ -12021,7 +12021,7 @@
       </c>
       <c r="H190" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Antofagasta </t>
+          <t>Antofagasta</t>
         </is>
       </c>
       <c r="I190" t="inlineStr">
@@ -12082,7 +12082,7 @@
       </c>
       <c r="H191" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Biobío </t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I191" t="inlineStr">
@@ -12204,7 +12204,7 @@
       </c>
       <c r="H193" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Maule </t>
+          <t>Maule</t>
         </is>
       </c>
       <c r="I193" t="inlineStr">
@@ -12265,7 +12265,7 @@
       </c>
       <c r="H194" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I194" t="inlineStr">
@@ -12326,7 +12326,7 @@
       </c>
       <c r="H195" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Valparaíso </t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I195" t="inlineStr">
@@ -12387,7 +12387,7 @@
       </c>
       <c r="H196" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I196" t="inlineStr">
@@ -12448,7 +12448,7 @@
       </c>
       <c r="H197" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I197" t="inlineStr">
@@ -12570,7 +12570,7 @@
       </c>
       <c r="H199" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I199" t="inlineStr">
@@ -12631,7 +12631,7 @@
       </c>
       <c r="H200" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de la Araucanía </t>
+          <t>Araucanía</t>
         </is>
       </c>
       <c r="I200" t="inlineStr">
@@ -12692,7 +12692,7 @@
       </c>
       <c r="H201" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I201" t="inlineStr">
@@ -12753,7 +12753,7 @@
       </c>
       <c r="H202" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Biobío </t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I202" t="inlineStr">
@@ -12814,7 +12814,7 @@
       </c>
       <c r="H203" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I203" t="inlineStr">
@@ -12875,7 +12875,7 @@
       </c>
       <c r="H204" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Biobío </t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I204" t="inlineStr">
@@ -12936,7 +12936,7 @@
       </c>
       <c r="H205" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Biobío </t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I205" t="inlineStr">
@@ -12997,7 +12997,7 @@
       </c>
       <c r="H206" t="inlineStr">
         <is>
-          <t>Región Aysén del General Carlos Ibáñez del Campo</t>
+          <t>Aysén</t>
         </is>
       </c>
       <c r="I206" t="inlineStr">
@@ -13058,7 +13058,7 @@
       </c>
       <c r="H207" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I207" t="inlineStr">
@@ -13119,7 +13119,7 @@
       </c>
       <c r="H208" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de la Araucanía </t>
+          <t>Araucanía</t>
         </is>
       </c>
       <c r="I208" t="inlineStr">
@@ -13180,7 +13180,7 @@
       </c>
       <c r="H209" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Biobío </t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I209" t="inlineStr">
@@ -13241,7 +13241,7 @@
       </c>
       <c r="H210" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I210" t="inlineStr">
@@ -13302,7 +13302,7 @@
       </c>
       <c r="H211" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I211" t="inlineStr">
@@ -13363,7 +13363,7 @@
       </c>
       <c r="H212" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Maule </t>
+          <t>Maule</t>
         </is>
       </c>
       <c r="I212" t="inlineStr">
@@ -13424,7 +13424,7 @@
       </c>
       <c r="H213" t="inlineStr">
         <is>
-          <t>Región del Libertador General Bernardo O´Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I213" t="inlineStr">
@@ -13485,7 +13485,7 @@
       </c>
       <c r="H214" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I214" t="inlineStr">
@@ -13546,7 +13546,7 @@
       </c>
       <c r="H215" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Biobío </t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I215" t="inlineStr">
@@ -13607,7 +13607,7 @@
       </c>
       <c r="H216" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I216" t="inlineStr">
@@ -13668,7 +13668,7 @@
       </c>
       <c r="H217" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I217" t="inlineStr">
@@ -13729,7 +13729,7 @@
       </c>
       <c r="H218" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Maule </t>
+          <t>Maule</t>
         </is>
       </c>
       <c r="I218" t="inlineStr">
@@ -13790,7 +13790,7 @@
       </c>
       <c r="H219" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de la Araucanía </t>
+          <t>Araucanía</t>
         </is>
       </c>
       <c r="I219" t="inlineStr">
@@ -13851,7 +13851,7 @@
       </c>
       <c r="H220" t="inlineStr">
         <is>
-          <t>Región del Ñuble</t>
+          <t>Ñuble</t>
         </is>
       </c>
       <c r="I220" t="inlineStr">
@@ -13912,7 +13912,7 @@
       </c>
       <c r="H221" t="inlineStr">
         <is>
-          <t>Región de Magallanes y de la Antártica</t>
+          <t>Magallanes</t>
         </is>
       </c>
       <c r="I221" t="inlineStr">
@@ -13973,7 +13973,7 @@
       </c>
       <c r="H222" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I222" t="inlineStr">
@@ -14034,7 +14034,7 @@
       </c>
       <c r="H223" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Valparaíso </t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I223" t="inlineStr">
@@ -14095,7 +14095,7 @@
       </c>
       <c r="H224" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Coquimbo </t>
+          <t>Coquimbo</t>
         </is>
       </c>
       <c r="I224" t="inlineStr">
@@ -14156,7 +14156,7 @@
       </c>
       <c r="H225" t="inlineStr">
         <is>
-          <t>Región de Los Ríos</t>
+          <t>Los Ríos</t>
         </is>
       </c>
       <c r="I225" t="inlineStr">
@@ -14217,7 +14217,7 @@
       </c>
       <c r="H226" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Biobío </t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I226" t="inlineStr">
@@ -14278,7 +14278,7 @@
       </c>
       <c r="H227" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I227" t="inlineStr">
@@ -14339,7 +14339,7 @@
       </c>
       <c r="H228" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Biobío </t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I228" t="inlineStr">
@@ -14400,7 +14400,7 @@
       </c>
       <c r="H229" t="inlineStr">
         <is>
-          <t>Región del Libertador General Bernardo O´Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I229" t="inlineStr">
@@ -14461,7 +14461,7 @@
       </c>
       <c r="H230" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Valparaíso </t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I230" t="inlineStr">
@@ -14522,7 +14522,7 @@
       </c>
       <c r="H231" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Valparaíso </t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I231" t="inlineStr">
@@ -14583,7 +14583,7 @@
       </c>
       <c r="H232" t="inlineStr">
         <is>
-          <t>Región de Los Ríos</t>
+          <t>Los Ríos</t>
         </is>
       </c>
       <c r="I232" t="inlineStr">
@@ -14644,7 +14644,7 @@
       </c>
       <c r="H233" t="inlineStr">
         <is>
-          <t>Región del Ñuble</t>
+          <t>Ñuble</t>
         </is>
       </c>
       <c r="I233" t="inlineStr">
@@ -14705,7 +14705,7 @@
       </c>
       <c r="H234" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Atacama </t>
+          <t>Atacama</t>
         </is>
       </c>
       <c r="I234" t="inlineStr">
@@ -14827,7 +14827,7 @@
       </c>
       <c r="H236" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Maule </t>
+          <t>Maule</t>
         </is>
       </c>
       <c r="I236" t="inlineStr">
@@ -14888,7 +14888,7 @@
       </c>
       <c r="H237" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de la Araucanía </t>
+          <t>Araucanía</t>
         </is>
       </c>
       <c r="I237" t="inlineStr">
@@ -14949,7 +14949,7 @@
       </c>
       <c r="H238" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Atacama </t>
+          <t>Atacama</t>
         </is>
       </c>
       <c r="I238" t="inlineStr">
@@ -15010,7 +15010,7 @@
       </c>
       <c r="H239" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I239" t="inlineStr">
@@ -15071,7 +15071,7 @@
       </c>
       <c r="H240" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Maule </t>
+          <t>Maule</t>
         </is>
       </c>
       <c r="I240" t="inlineStr">
@@ -15132,7 +15132,7 @@
       </c>
       <c r="H241" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de la Araucanía </t>
+          <t>Araucanía</t>
         </is>
       </c>
       <c r="I241" t="inlineStr">
@@ -15193,7 +15193,7 @@
       </c>
       <c r="H242" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de la Araucanía </t>
+          <t>Araucanía</t>
         </is>
       </c>
       <c r="I242" t="inlineStr">
@@ -15254,7 +15254,7 @@
       </c>
       <c r="H243" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I243" t="inlineStr">
@@ -15315,7 +15315,7 @@
       </c>
       <c r="H244" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Atacama </t>
+          <t>Atacama</t>
         </is>
       </c>
       <c r="I244" t="inlineStr">
@@ -15376,7 +15376,7 @@
       </c>
       <c r="H245" t="inlineStr">
         <is>
-          <t>Región del Libertador General Bernardo O´Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I245" t="inlineStr">
@@ -15437,7 +15437,7 @@
       </c>
       <c r="H246" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Valparaíso </t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I246" t="inlineStr">
@@ -15559,7 +15559,7 @@
       </c>
       <c r="H248" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Antofagasta </t>
+          <t>Antofagasta</t>
         </is>
       </c>
       <c r="I248" t="inlineStr">
@@ -15681,7 +15681,7 @@
       </c>
       <c r="H250" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Valparaíso </t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I250" t="inlineStr">
@@ -15742,7 +15742,7 @@
       </c>
       <c r="H251" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Maule </t>
+          <t>Maule</t>
         </is>
       </c>
       <c r="I251" t="inlineStr">
@@ -15803,7 +15803,7 @@
       </c>
       <c r="H252" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Coquimbo </t>
+          <t>Coquimbo</t>
         </is>
       </c>
       <c r="I252" t="inlineStr">
@@ -15864,7 +15864,7 @@
       </c>
       <c r="H253" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Coquimbo </t>
+          <t>Coquimbo</t>
         </is>
       </c>
       <c r="I253" t="inlineStr">
@@ -15925,7 +15925,7 @@
       </c>
       <c r="H254" t="inlineStr">
         <is>
-          <t>Región del Libertador General Bernardo O´Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I254" t="inlineStr">
@@ -15986,7 +15986,7 @@
       </c>
       <c r="H255" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de los Lagos </t>
+          <t>Los Lagos</t>
         </is>
       </c>
       <c r="I255" t="inlineStr">
@@ -16047,7 +16047,7 @@
       </c>
       <c r="H256" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I256" t="inlineStr">
@@ -16108,7 +16108,7 @@
       </c>
       <c r="H257" t="inlineStr">
         <is>
-          <t>Región del Libertador General Bernardo O´Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I257" t="inlineStr">
@@ -16169,7 +16169,7 @@
       </c>
       <c r="H258" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Maule </t>
+          <t>Maule</t>
         </is>
       </c>
       <c r="I258" t="inlineStr">
@@ -16230,7 +16230,7 @@
       </c>
       <c r="H259" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Valparaíso </t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I259" t="inlineStr">
@@ -16291,7 +16291,7 @@
       </c>
       <c r="H260" t="inlineStr">
         <is>
-          <t>Región del Libertador General Bernardo O´Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I260" t="inlineStr">
@@ -16352,7 +16352,7 @@
       </c>
       <c r="H261" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Maule </t>
+          <t>Maule</t>
         </is>
       </c>
       <c r="I261" t="inlineStr">
@@ -16413,7 +16413,7 @@
       </c>
       <c r="H262" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Maule </t>
+          <t>Maule</t>
         </is>
       </c>
       <c r="I262" t="inlineStr">
@@ -16474,7 +16474,7 @@
       </c>
       <c r="H263" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I263" t="inlineStr">
@@ -16535,7 +16535,7 @@
       </c>
       <c r="H264" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Valparaíso </t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I264" t="inlineStr">
@@ -16596,7 +16596,7 @@
       </c>
       <c r="H265" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I265" t="inlineStr">
@@ -16657,7 +16657,7 @@
       </c>
       <c r="H266" t="inlineStr">
         <is>
-          <t>Región del Ñuble</t>
+          <t>Ñuble</t>
         </is>
       </c>
       <c r="I266" t="inlineStr">
@@ -16779,7 +16779,7 @@
       </c>
       <c r="H268" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I268" t="inlineStr">
@@ -16840,7 +16840,7 @@
       </c>
       <c r="H269" t="inlineStr">
         <is>
-          <t>Región del Ñuble</t>
+          <t>Ñuble</t>
         </is>
       </c>
       <c r="I269" t="inlineStr">
@@ -16901,7 +16901,7 @@
       </c>
       <c r="H270" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de los Lagos </t>
+          <t>Los Lagos</t>
         </is>
       </c>
       <c r="I270" t="inlineStr">
@@ -16962,7 +16962,7 @@
       </c>
       <c r="H271" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I271" t="inlineStr">
@@ -17023,7 +17023,7 @@
       </c>
       <c r="H272" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Biobío </t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I272" t="inlineStr">
@@ -17084,7 +17084,7 @@
       </c>
       <c r="H273" t="inlineStr">
         <is>
-          <t>Región del Ñuble</t>
+          <t>Ñuble</t>
         </is>
       </c>
       <c r="I273" t="inlineStr">
@@ -17145,7 +17145,7 @@
       </c>
       <c r="H274" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de la Araucanía </t>
+          <t>Araucanía</t>
         </is>
       </c>
       <c r="I274" t="inlineStr">
@@ -17206,7 +17206,7 @@
       </c>
       <c r="H275" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I275" t="inlineStr">
@@ -17267,7 +17267,7 @@
       </c>
       <c r="H276" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Biobío </t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I276" t="inlineStr">
@@ -17328,7 +17328,7 @@
       </c>
       <c r="H277" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Coquimbo </t>
+          <t>Coquimbo</t>
         </is>
       </c>
       <c r="I277" t="inlineStr">
@@ -17389,7 +17389,7 @@
       </c>
       <c r="H278" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de la Araucanía </t>
+          <t>Araucanía</t>
         </is>
       </c>
       <c r="I278" t="inlineStr">
@@ -17450,7 +17450,7 @@
       </c>
       <c r="H279" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Biobío </t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I279" t="inlineStr">
@@ -17572,7 +17572,7 @@
       </c>
       <c r="H281" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de la Araucanía </t>
+          <t>Araucanía</t>
         </is>
       </c>
       <c r="I281" t="inlineStr">
@@ -17633,7 +17633,7 @@
       </c>
       <c r="H282" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I282" t="inlineStr">
@@ -17694,7 +17694,7 @@
       </c>
       <c r="H283" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Coquimbo </t>
+          <t>Coquimbo</t>
         </is>
       </c>
       <c r="I283" t="inlineStr">
@@ -17755,7 +17755,7 @@
       </c>
       <c r="H284" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Biobío </t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I284" t="inlineStr">
@@ -17816,7 +17816,7 @@
       </c>
       <c r="H285" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Atacama </t>
+          <t>Atacama</t>
         </is>
       </c>
       <c r="I285" t="inlineStr">
@@ -17938,7 +17938,7 @@
       </c>
       <c r="H287" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Maule </t>
+          <t>Maule</t>
         </is>
       </c>
       <c r="I287" t="inlineStr">
@@ -17999,7 +17999,7 @@
       </c>
       <c r="H288" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Valparaíso </t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I288" t="inlineStr">
@@ -18060,7 +18060,7 @@
       </c>
       <c r="H289" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Atacama </t>
+          <t>Atacama</t>
         </is>
       </c>
       <c r="I289" t="inlineStr">
@@ -18121,7 +18121,7 @@
       </c>
       <c r="H290" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de la Araucanía </t>
+          <t>Araucanía</t>
         </is>
       </c>
       <c r="I290" t="inlineStr">
@@ -18182,7 +18182,7 @@
       </c>
       <c r="H291" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Coquimbo </t>
+          <t>Coquimbo</t>
         </is>
       </c>
       <c r="I291" t="inlineStr">
@@ -18243,7 +18243,7 @@
       </c>
       <c r="H292" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I292" t="inlineStr">
@@ -18304,7 +18304,7 @@
       </c>
       <c r="H293" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I293" t="inlineStr">
@@ -18365,7 +18365,7 @@
       </c>
       <c r="H294" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I294" t="inlineStr">
@@ -18426,7 +18426,7 @@
       </c>
       <c r="H295" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I295" t="inlineStr">
@@ -18487,7 +18487,7 @@
       </c>
       <c r="H296" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I296" t="inlineStr">
@@ -18548,7 +18548,7 @@
       </c>
       <c r="H297" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Coquimbo </t>
+          <t>Coquimbo</t>
         </is>
       </c>
       <c r="I297" t="inlineStr">
@@ -18609,7 +18609,7 @@
       </c>
       <c r="H298" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Valparaíso </t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I298" t="inlineStr">
@@ -18670,7 +18670,7 @@
       </c>
       <c r="H299" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Coquimbo </t>
+          <t>Coquimbo</t>
         </is>
       </c>
       <c r="I299" t="inlineStr">
@@ -18731,7 +18731,7 @@
       </c>
       <c r="H300" t="inlineStr">
         <is>
-          <t>Región de Los Ríos</t>
+          <t>Los Ríos</t>
         </is>
       </c>
       <c r="I300" t="inlineStr">
@@ -18792,7 +18792,7 @@
       </c>
       <c r="H301" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de la Araucanía </t>
+          <t>Araucanía</t>
         </is>
       </c>
       <c r="I301" t="inlineStr">
@@ -18853,7 +18853,7 @@
       </c>
       <c r="H302" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Biobío </t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I302" t="inlineStr">
@@ -18914,7 +18914,7 @@
       </c>
       <c r="H303" t="inlineStr">
         <is>
-          <t>Región del Libertador General Bernardo O´Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I303" t="inlineStr">
@@ -18975,7 +18975,7 @@
       </c>
       <c r="H304" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de la Araucanía </t>
+          <t>Araucanía</t>
         </is>
       </c>
       <c r="I304" t="inlineStr">
@@ -19036,7 +19036,7 @@
       </c>
       <c r="H305" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Atacama </t>
+          <t>Atacama</t>
         </is>
       </c>
       <c r="I305" t="inlineStr">
@@ -19097,7 +19097,7 @@
       </c>
       <c r="H306" t="inlineStr">
         <is>
-          <t>Región del Libertador General Bernardo O´Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I306" t="inlineStr">
@@ -19158,7 +19158,7 @@
       </c>
       <c r="H307" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Coquimbo </t>
+          <t>Coquimbo</t>
         </is>
       </c>
       <c r="I307" t="inlineStr">
@@ -19219,7 +19219,7 @@
       </c>
       <c r="H308" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Valparaíso </t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I308" t="inlineStr">
@@ -19402,7 +19402,7 @@
       </c>
       <c r="H311" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I311" t="inlineStr">
@@ -19463,7 +19463,7 @@
       </c>
       <c r="H312" t="inlineStr">
         <is>
-          <t>Región de Los Ríos</t>
+          <t>Los Ríos</t>
         </is>
       </c>
       <c r="I312" t="inlineStr">
@@ -19524,7 +19524,7 @@
       </c>
       <c r="H313" t="inlineStr">
         <is>
-          <t>Región del Ñuble</t>
+          <t>Ñuble</t>
         </is>
       </c>
       <c r="I313" t="inlineStr">
@@ -19585,7 +19585,7 @@
       </c>
       <c r="H314" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de la Araucanía </t>
+          <t>Araucanía</t>
         </is>
       </c>
       <c r="I314" t="inlineStr">
@@ -19646,7 +19646,7 @@
       </c>
       <c r="H315" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de la Araucanía </t>
+          <t>Araucanía</t>
         </is>
       </c>
       <c r="I315" t="inlineStr">
@@ -19707,7 +19707,7 @@
       </c>
       <c r="H316" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I316" t="inlineStr">
@@ -19829,7 +19829,7 @@
       </c>
       <c r="H318" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Valparaíso </t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I318" t="inlineStr">
@@ -19890,7 +19890,7 @@
       </c>
       <c r="H319" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Valparaíso </t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I319" t="inlineStr">
@@ -19951,7 +19951,7 @@
       </c>
       <c r="H320" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I320" t="inlineStr">
@@ -20012,7 +20012,7 @@
       </c>
       <c r="H321" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de los Lagos </t>
+          <t>Los Lagos</t>
         </is>
       </c>
       <c r="I321" t="inlineStr">
@@ -20073,7 +20073,7 @@
       </c>
       <c r="H322" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Valparaíso </t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I322" t="inlineStr">
@@ -20134,7 +20134,7 @@
       </c>
       <c r="H323" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I323" t="inlineStr">
@@ -20195,7 +20195,7 @@
       </c>
       <c r="H324" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Biobío </t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I324" t="inlineStr">
@@ -20317,7 +20317,7 @@
       </c>
       <c r="H326" t="inlineStr">
         <is>
-          <t>Región del Libertador General Bernardo O´Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I326" t="inlineStr">
@@ -20378,7 +20378,7 @@
       </c>
       <c r="H327" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Valparaíso </t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I327" t="inlineStr">
@@ -20439,7 +20439,7 @@
       </c>
       <c r="H328" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de la Araucanía </t>
+          <t>Araucanía</t>
         </is>
       </c>
       <c r="I328" t="inlineStr">
@@ -20500,7 +20500,7 @@
       </c>
       <c r="H329" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I329" t="inlineStr">
@@ -20561,7 +20561,7 @@
       </c>
       <c r="H330" t="inlineStr">
         <is>
-          <t>Región del Ñuble</t>
+          <t>Ñuble</t>
         </is>
       </c>
       <c r="I330" t="inlineStr">
@@ -20683,7 +20683,7 @@
       </c>
       <c r="H332" t="inlineStr">
         <is>
-          <t>Región del Libertador General Bernardo O´Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I332" t="inlineStr">
@@ -20805,7 +20805,7 @@
       </c>
       <c r="H334" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de la Araucanía </t>
+          <t>Araucanía</t>
         </is>
       </c>
       <c r="I334" t="inlineStr">
@@ -20866,7 +20866,7 @@
       </c>
       <c r="H335" t="inlineStr">
         <is>
-          <t>Región del Libertador General Bernardo O´Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I335" t="inlineStr">
@@ -20927,7 +20927,7 @@
       </c>
       <c r="H336" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Antofagasta </t>
+          <t>Antofagasta</t>
         </is>
       </c>
       <c r="I336" t="inlineStr">
@@ -20988,7 +20988,7 @@
       </c>
       <c r="H337" t="inlineStr">
         <is>
-          <t>Región del Libertador General Bernardo O´Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I337" t="inlineStr">
@@ -21049,7 +21049,7 @@
       </c>
       <c r="H338" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I338" t="inlineStr">
@@ -21110,7 +21110,7 @@
       </c>
       <c r="H339" t="inlineStr">
         <is>
-          <t>Región de Magallanes y de la Antártica</t>
+          <t>Magallanes</t>
         </is>
       </c>
       <c r="I339" t="inlineStr">
@@ -21171,7 +21171,7 @@
       </c>
       <c r="H340" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I340" t="inlineStr">
@@ -21232,7 +21232,7 @@
       </c>
       <c r="H341" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de la Araucanía </t>
+          <t>Araucanía</t>
         </is>
       </c>
       <c r="I341" t="inlineStr">
@@ -21293,7 +21293,7 @@
       </c>
       <c r="H342" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I342" t="inlineStr">
@@ -21354,7 +21354,7 @@
       </c>
       <c r="H343" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I343" t="inlineStr">
@@ -21415,7 +21415,7 @@
       </c>
       <c r="H344" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Valparaíso </t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I344" t="inlineStr">
@@ -21537,7 +21537,7 @@
       </c>
       <c r="H346" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Valparaíso </t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I346" t="inlineStr">
@@ -21598,7 +21598,7 @@
       </c>
       <c r="H347" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Atacama </t>
+          <t>Atacama</t>
         </is>
       </c>
       <c r="I347" t="inlineStr">
@@ -21659,7 +21659,7 @@
       </c>
       <c r="H348" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Valparaíso </t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I348" t="inlineStr">
@@ -21720,7 +21720,7 @@
       </c>
       <c r="H349" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I349" t="inlineStr">
@@ -21781,7 +21781,7 @@
       </c>
       <c r="H350" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I350" t="inlineStr">
@@ -21842,7 +21842,7 @@
       </c>
       <c r="H351" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Biobío </t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I351" t="inlineStr">
@@ -21903,7 +21903,7 @@
       </c>
       <c r="H352" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I352" t="inlineStr">
@@ -21964,7 +21964,7 @@
       </c>
       <c r="H353" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Biobío </t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I353" t="inlineStr">
@@ -22086,7 +22086,7 @@
       </c>
       <c r="H355" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I355" t="inlineStr">
@@ -22147,7 +22147,7 @@
       </c>
       <c r="H356" t="inlineStr">
         <is>
-          <t>Región de Arica y Parinacota</t>
+          <t>Arica y Parinacota</t>
         </is>
       </c>
       <c r="I356" t="inlineStr">
@@ -22269,7 +22269,7 @@
       </c>
       <c r="H358" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I358" t="inlineStr">
@@ -22330,7 +22330,7 @@
       </c>
       <c r="H359" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Biobío </t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I359" t="inlineStr">
@@ -22391,7 +22391,7 @@
       </c>
       <c r="H360" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I360" t="inlineStr">
@@ -22452,7 +22452,7 @@
       </c>
       <c r="H361" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Valparaíso </t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I361" t="inlineStr">
@@ -22513,7 +22513,7 @@
       </c>
       <c r="H362" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I362" t="inlineStr">
@@ -22574,7 +22574,7 @@
       </c>
       <c r="H363" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I363" t="inlineStr">
@@ -22635,7 +22635,7 @@
       </c>
       <c r="H364" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I364" t="inlineStr">
@@ -22696,7 +22696,7 @@
       </c>
       <c r="H365" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I365" t="inlineStr">
@@ -22757,7 +22757,7 @@
       </c>
       <c r="H366" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I366" t="inlineStr">
@@ -22818,7 +22818,7 @@
       </c>
       <c r="H367" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Maule </t>
+          <t>Maule</t>
         </is>
       </c>
       <c r="I367" t="inlineStr">
@@ -22879,7 +22879,7 @@
       </c>
       <c r="H368" t="inlineStr">
         <is>
-          <t>Región del Ñuble</t>
+          <t>Ñuble</t>
         </is>
       </c>
       <c r="I368" t="inlineStr">
@@ -22940,7 +22940,7 @@
       </c>
       <c r="H369" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Coquimbo </t>
+          <t>Coquimbo</t>
         </is>
       </c>
       <c r="I369" t="inlineStr">
@@ -23001,7 +23001,7 @@
       </c>
       <c r="H370" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I370" t="inlineStr">
@@ -23062,7 +23062,7 @@
       </c>
       <c r="H371" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I371" t="inlineStr">
@@ -23184,7 +23184,7 @@
       </c>
       <c r="H373" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de los Lagos </t>
+          <t>Los Lagos</t>
         </is>
       </c>
       <c r="I373" t="inlineStr">
@@ -23245,7 +23245,7 @@
       </c>
       <c r="H374" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Biobío </t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I374" t="inlineStr">
@@ -23306,7 +23306,7 @@
       </c>
       <c r="H375" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Valparaíso </t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I375" t="inlineStr">
@@ -23367,7 +23367,7 @@
       </c>
       <c r="H376" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de la Araucanía </t>
+          <t>Araucanía</t>
         </is>
       </c>
       <c r="I376" t="inlineStr">
@@ -23428,7 +23428,7 @@
       </c>
       <c r="H377" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I377" t="inlineStr">
@@ -23489,7 +23489,7 @@
       </c>
       <c r="H378" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de la Araucanía </t>
+          <t>Araucanía</t>
         </is>
       </c>
       <c r="I378" t="inlineStr">
@@ -23550,7 +23550,7 @@
       </c>
       <c r="H379" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Valparaíso </t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I379" t="inlineStr">
@@ -23611,7 +23611,7 @@
       </c>
       <c r="H380" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I380" t="inlineStr">
@@ -23672,7 +23672,7 @@
       </c>
       <c r="H381" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Valparaíso </t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I381" t="inlineStr">
@@ -23794,7 +23794,7 @@
       </c>
       <c r="H383" t="inlineStr">
         <is>
-          <t>Región de Los Ríos</t>
+          <t>Los Ríos</t>
         </is>
       </c>
       <c r="I383" t="inlineStr">
@@ -23855,7 +23855,7 @@
       </c>
       <c r="H384" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I384" t="inlineStr">
@@ -23916,7 +23916,7 @@
       </c>
       <c r="H385" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I385" t="inlineStr">
@@ -23977,7 +23977,7 @@
       </c>
       <c r="H386" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Valparaíso </t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I386" t="inlineStr">
@@ -24038,7 +24038,7 @@
       </c>
       <c r="H387" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I387" t="inlineStr">
@@ -24099,7 +24099,7 @@
       </c>
       <c r="H388" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Antofagasta </t>
+          <t>Antofagasta</t>
         </is>
       </c>
       <c r="I388" t="inlineStr">
@@ -24160,7 +24160,7 @@
       </c>
       <c r="H389" t="inlineStr">
         <is>
-          <t>Región de Arica y Parinacota</t>
+          <t>Arica y Parinacota</t>
         </is>
       </c>
       <c r="I389" t="inlineStr">
@@ -24221,7 +24221,7 @@
       </c>
       <c r="H390" t="inlineStr">
         <is>
-          <t>Región del Libertador General Bernardo O´Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I390" t="inlineStr">
@@ -24282,7 +24282,7 @@
       </c>
       <c r="H391" t="inlineStr">
         <is>
-          <t>Región de Arica y Parinacota</t>
+          <t>Arica y Parinacota</t>
         </is>
       </c>
       <c r="I391" t="inlineStr">
@@ -24343,7 +24343,7 @@
       </c>
       <c r="H392" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I392" t="inlineStr">
@@ -24404,7 +24404,7 @@
       </c>
       <c r="H393" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Valparaíso </t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I393" t="inlineStr">
@@ -24465,7 +24465,7 @@
       </c>
       <c r="H394" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de los Lagos </t>
+          <t>Los Lagos</t>
         </is>
       </c>
       <c r="I394" t="inlineStr">
@@ -24526,7 +24526,7 @@
       </c>
       <c r="H395" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I395" t="inlineStr">
@@ -24587,7 +24587,7 @@
       </c>
       <c r="H396" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Valparaíso </t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I396" t="inlineStr">
@@ -24648,7 +24648,7 @@
       </c>
       <c r="H397" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I397" t="inlineStr">
@@ -24709,7 +24709,7 @@
       </c>
       <c r="H398" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Tarapacá  </t>
+          <t>Tarapacá</t>
         </is>
       </c>
       <c r="I398" t="inlineStr">
@@ -24770,7 +24770,7 @@
       </c>
       <c r="H399" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de la Araucanía </t>
+          <t>Araucanía</t>
         </is>
       </c>
       <c r="I399" t="inlineStr">
@@ -24831,7 +24831,7 @@
       </c>
       <c r="H400" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I400" t="inlineStr">
@@ -24892,7 +24892,7 @@
       </c>
       <c r="H401" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de la Araucanía </t>
+          <t>Araucanía</t>
         </is>
       </c>
       <c r="I401" t="inlineStr">
@@ -24953,7 +24953,7 @@
       </c>
       <c r="H402" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Biobío </t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I402" t="inlineStr">
@@ -25014,7 +25014,7 @@
       </c>
       <c r="H403" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I403" t="inlineStr">
@@ -25075,7 +25075,7 @@
       </c>
       <c r="H404" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Coquimbo </t>
+          <t>Coquimbo</t>
         </is>
       </c>
       <c r="I404" t="inlineStr">
@@ -25136,7 +25136,7 @@
       </c>
       <c r="H405" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de los Lagos </t>
+          <t>Los Lagos</t>
         </is>
       </c>
       <c r="I405" t="inlineStr">
@@ -25197,7 +25197,7 @@
       </c>
       <c r="H406" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Tarapacá  </t>
+          <t>Tarapacá</t>
         </is>
       </c>
       <c r="I406" t="inlineStr">
@@ -25258,7 +25258,7 @@
       </c>
       <c r="H407" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Biobío </t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I407" t="inlineStr">
@@ -25319,7 +25319,7 @@
       </c>
       <c r="H408" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Tarapacá  </t>
+          <t>Tarapacá</t>
         </is>
       </c>
       <c r="I408" t="inlineStr">
@@ -25380,7 +25380,7 @@
       </c>
       <c r="H409" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Biobío </t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I409" t="inlineStr">
@@ -25441,7 +25441,7 @@
       </c>
       <c r="H410" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Coquimbo </t>
+          <t>Coquimbo</t>
         </is>
       </c>
       <c r="I410" t="inlineStr">
@@ -25502,7 +25502,7 @@
       </c>
       <c r="H411" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I411" t="inlineStr">
@@ -25563,7 +25563,7 @@
       </c>
       <c r="H412" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de los Lagos </t>
+          <t>Los Lagos</t>
         </is>
       </c>
       <c r="I412" t="inlineStr">
@@ -25624,7 +25624,7 @@
       </c>
       <c r="H413" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Coquimbo </t>
+          <t>Coquimbo</t>
         </is>
       </c>
       <c r="I413" t="inlineStr">
@@ -25746,7 +25746,7 @@
       </c>
       <c r="H415" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Atacama </t>
+          <t>Atacama</t>
         </is>
       </c>
       <c r="I415" t="inlineStr">
@@ -25807,7 +25807,7 @@
       </c>
       <c r="H416" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Biobío </t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I416" t="inlineStr">
@@ -25868,7 +25868,7 @@
       </c>
       <c r="H417" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Biobío </t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I417" t="inlineStr">
@@ -25929,7 +25929,7 @@
       </c>
       <c r="H418" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de los Lagos </t>
+          <t>Los Lagos</t>
         </is>
       </c>
       <c r="I418" t="inlineStr">
@@ -25990,7 +25990,7 @@
       </c>
       <c r="H419" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Biobío </t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I419" t="inlineStr">
@@ -26051,7 +26051,7 @@
       </c>
       <c r="H420" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Coquimbo </t>
+          <t>Coquimbo</t>
         </is>
       </c>
       <c r="I420" t="inlineStr">
@@ -26112,7 +26112,7 @@
       </c>
       <c r="H421" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I421" t="inlineStr">
@@ -26173,7 +26173,7 @@
       </c>
       <c r="H422" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Valparaíso </t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I422" t="inlineStr">
@@ -26234,7 +26234,7 @@
       </c>
       <c r="H423" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I423" t="inlineStr">
@@ -26295,7 +26295,7 @@
       </c>
       <c r="H424" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Valparaíso </t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I424" t="inlineStr">
@@ -26356,7 +26356,7 @@
       </c>
       <c r="H425" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de los Lagos </t>
+          <t>Los Lagos</t>
         </is>
       </c>
       <c r="I425" t="inlineStr">
@@ -26417,7 +26417,7 @@
       </c>
       <c r="H426" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Maule </t>
+          <t>Maule</t>
         </is>
       </c>
       <c r="I426" t="inlineStr">
@@ -26478,7 +26478,7 @@
       </c>
       <c r="H427" t="inlineStr">
         <is>
-          <t>Región de Magallanes y de la Antártica</t>
+          <t>Magallanes</t>
         </is>
       </c>
       <c r="I427" t="inlineStr">
@@ -26539,7 +26539,7 @@
       </c>
       <c r="H428" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Tarapacá  </t>
+          <t>Tarapacá</t>
         </is>
       </c>
       <c r="I428" t="inlineStr">
@@ -26600,7 +26600,7 @@
       </c>
       <c r="H429" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I429" t="inlineStr">
@@ -26722,7 +26722,7 @@
       </c>
       <c r="H431" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de la Araucanía </t>
+          <t>Araucanía</t>
         </is>
       </c>
       <c r="I431" t="inlineStr">
@@ -26783,7 +26783,7 @@
       </c>
       <c r="H432" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I432" t="inlineStr">
@@ -26844,7 +26844,7 @@
       </c>
       <c r="H433" t="inlineStr">
         <is>
-          <t>Región de Magallanes y de la Antártica</t>
+          <t>Magallanes</t>
         </is>
       </c>
       <c r="I433" t="inlineStr">
@@ -26905,7 +26905,7 @@
       </c>
       <c r="H434" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Biobío </t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I434" t="inlineStr">
@@ -26966,7 +26966,7 @@
       </c>
       <c r="H435" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de la Araucanía </t>
+          <t>Araucanía</t>
         </is>
       </c>
       <c r="I435" t="inlineStr">
@@ -27027,7 +27027,7 @@
       </c>
       <c r="H436" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I436" t="inlineStr">
@@ -27088,7 +27088,7 @@
       </c>
       <c r="H437" t="inlineStr">
         <is>
-          <t>Región de Los Ríos</t>
+          <t>Los Ríos</t>
         </is>
       </c>
       <c r="I437" t="inlineStr">
@@ -27149,7 +27149,7 @@
       </c>
       <c r="H438" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Maule </t>
+          <t>Maule</t>
         </is>
       </c>
       <c r="I438" t="inlineStr">
@@ -27210,7 +27210,7 @@
       </c>
       <c r="H439" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Antofagasta </t>
+          <t>Antofagasta</t>
         </is>
       </c>
       <c r="I439" t="inlineStr">
@@ -27271,7 +27271,7 @@
       </c>
       <c r="H440" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I440" t="inlineStr">
@@ -27332,7 +27332,7 @@
       </c>
       <c r="H441" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Coquimbo </t>
+          <t>Coquimbo</t>
         </is>
       </c>
       <c r="I441" t="inlineStr">
@@ -27393,7 +27393,7 @@
       </c>
       <c r="H442" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I442" t="inlineStr">
@@ -27454,7 +27454,7 @@
       </c>
       <c r="H443" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de la Araucanía </t>
+          <t>Araucanía</t>
         </is>
       </c>
       <c r="I443" t="inlineStr">
@@ -27576,7 +27576,7 @@
       </c>
       <c r="H445" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I445" t="inlineStr">
@@ -27637,7 +27637,7 @@
       </c>
       <c r="H446" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Coquimbo </t>
+          <t>Coquimbo</t>
         </is>
       </c>
       <c r="I446" t="inlineStr">
@@ -27698,7 +27698,7 @@
       </c>
       <c r="H447" t="inlineStr">
         <is>
-          <t>Región de Arica y Parinacota</t>
+          <t>Arica y Parinacota</t>
         </is>
       </c>
       <c r="I447" t="inlineStr">
@@ -27759,7 +27759,7 @@
       </c>
       <c r="H448" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Maule </t>
+          <t>Maule</t>
         </is>
       </c>
       <c r="I448" t="inlineStr">
@@ -27820,7 +27820,7 @@
       </c>
       <c r="H449" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de los Lagos </t>
+          <t>Los Lagos</t>
         </is>
       </c>
       <c r="I449" t="inlineStr">
@@ -27881,7 +27881,7 @@
       </c>
       <c r="H450" t="inlineStr">
         <is>
-          <t>Región del Libertador General Bernardo O´Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I450" t="inlineStr">
@@ -27942,7 +27942,7 @@
       </c>
       <c r="H451" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Biobío </t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I451" t="inlineStr">
@@ -28003,7 +28003,7 @@
       </c>
       <c r="H452" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I452" t="inlineStr">
@@ -28064,7 +28064,7 @@
       </c>
       <c r="H453" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Biobío </t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I453" t="inlineStr">
@@ -28125,7 +28125,7 @@
       </c>
       <c r="H454" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I454" t="inlineStr">
@@ -28186,7 +28186,7 @@
       </c>
       <c r="H455" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Maule </t>
+          <t>Maule</t>
         </is>
       </c>
       <c r="I455" t="inlineStr">
@@ -28247,7 +28247,7 @@
       </c>
       <c r="H456" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I456" t="inlineStr">
@@ -28308,7 +28308,7 @@
       </c>
       <c r="H457" t="inlineStr">
         <is>
-          <t>Región Aysén del General Carlos Ibáñez del Campo</t>
+          <t>Aysén</t>
         </is>
       </c>
       <c r="I457" t="inlineStr">
@@ -28430,7 +28430,7 @@
       </c>
       <c r="H459" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I459" t="inlineStr">
@@ -28491,7 +28491,7 @@
       </c>
       <c r="H460" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de la Araucanía </t>
+          <t>Araucanía</t>
         </is>
       </c>
       <c r="I460" t="inlineStr">
@@ -28552,7 +28552,7 @@
       </c>
       <c r="H461" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Atacama </t>
+          <t>Atacama</t>
         </is>
       </c>
       <c r="I461" t="inlineStr">
@@ -28613,7 +28613,7 @@
       </c>
       <c r="H462" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Atacama </t>
+          <t>Atacama</t>
         </is>
       </c>
       <c r="I462" t="inlineStr">
@@ -28674,7 +28674,7 @@
       </c>
       <c r="H463" t="inlineStr">
         <is>
-          <t>Región de Los Ríos</t>
+          <t>Los Ríos</t>
         </is>
       </c>
       <c r="I463" t="inlineStr">
@@ -28735,7 +28735,7 @@
       </c>
       <c r="H464" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I464" t="inlineStr">
@@ -28796,7 +28796,7 @@
       </c>
       <c r="H465" t="inlineStr">
         <is>
-          <t>Región del Libertador General Bernardo O´Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I465" t="inlineStr">
@@ -28857,7 +28857,7 @@
       </c>
       <c r="H466" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Biobío </t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I466" t="inlineStr">
@@ -28918,7 +28918,7 @@
       </c>
       <c r="H467" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de los Lagos </t>
+          <t>Los Lagos</t>
         </is>
       </c>
       <c r="I467" t="inlineStr">
@@ -28979,7 +28979,7 @@
       </c>
       <c r="H468" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de la Araucanía </t>
+          <t>Araucanía</t>
         </is>
       </c>
       <c r="I468" t="inlineStr">
@@ -29040,7 +29040,7 @@
       </c>
       <c r="H469" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Coquimbo </t>
+          <t>Coquimbo</t>
         </is>
       </c>
       <c r="I469" t="inlineStr">
@@ -29101,7 +29101,7 @@
       </c>
       <c r="H470" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I470" t="inlineStr">
@@ -29162,7 +29162,7 @@
       </c>
       <c r="H471" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I471" t="inlineStr">
@@ -29223,7 +29223,7 @@
       </c>
       <c r="H472" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de la Araucanía </t>
+          <t>Araucanía</t>
         </is>
       </c>
       <c r="I472" t="inlineStr">
@@ -29284,7 +29284,7 @@
       </c>
       <c r="H473" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Biobío </t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I473" t="inlineStr">
@@ -29345,7 +29345,7 @@
       </c>
       <c r="H474" t="inlineStr">
         <is>
-          <t>Región del Libertador General Bernardo O´Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I474" t="inlineStr">
@@ -29406,7 +29406,7 @@
       </c>
       <c r="H475" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I475" t="inlineStr">
@@ -29467,7 +29467,7 @@
       </c>
       <c r="H476" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Valparaíso </t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I476" t="inlineStr">
@@ -29528,7 +29528,7 @@
       </c>
       <c r="H477" t="inlineStr">
         <is>
-          <t>Región de Magallanes y de la Antártica</t>
+          <t>Magallanes</t>
         </is>
       </c>
       <c r="I477" t="inlineStr">
@@ -29589,7 +29589,7 @@
       </c>
       <c r="H478" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de la Araucanía </t>
+          <t>Araucanía</t>
         </is>
       </c>
       <c r="I478" t="inlineStr">
@@ -29650,7 +29650,7 @@
       </c>
       <c r="H479" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de la Araucanía </t>
+          <t>Araucanía</t>
         </is>
       </c>
       <c r="I479" t="inlineStr">
@@ -29711,7 +29711,7 @@
       </c>
       <c r="H480" t="inlineStr">
         <is>
-          <t>Región del Libertador General Bernardo O´Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I480" t="inlineStr">
@@ -29772,7 +29772,7 @@
       </c>
       <c r="H481" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Antofagasta </t>
+          <t>Antofagasta</t>
         </is>
       </c>
       <c r="I481" t="inlineStr">
@@ -29833,7 +29833,7 @@
       </c>
       <c r="H482" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I482" t="inlineStr">
@@ -29894,7 +29894,7 @@
       </c>
       <c r="H483" t="inlineStr">
         <is>
-          <t>Región de Magallanes y de la Antártica</t>
+          <t>Magallanes</t>
         </is>
       </c>
       <c r="I483" t="inlineStr">
@@ -29955,7 +29955,7 @@
       </c>
       <c r="H484" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Antofagasta </t>
+          <t>Antofagasta</t>
         </is>
       </c>
       <c r="I484" t="inlineStr">
@@ -30077,7 +30077,7 @@
       </c>
       <c r="H486" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Coquimbo </t>
+          <t>Coquimbo</t>
         </is>
       </c>
       <c r="I486" t="inlineStr">
@@ -30138,7 +30138,7 @@
       </c>
       <c r="H487" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I487" t="inlineStr">
@@ -30199,7 +30199,7 @@
       </c>
       <c r="H488" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de los Lagos </t>
+          <t>Los Lagos</t>
         </is>
       </c>
       <c r="I488" t="inlineStr">
@@ -30260,7 +30260,7 @@
       </c>
       <c r="H489" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Biobío </t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I489" t="inlineStr">
@@ -30321,7 +30321,7 @@
       </c>
       <c r="H490" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Tarapacá  </t>
+          <t>Tarapacá</t>
         </is>
       </c>
       <c r="I490" t="inlineStr">
@@ -30382,7 +30382,7 @@
       </c>
       <c r="H491" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I491" t="inlineStr">
@@ -30443,7 +30443,7 @@
       </c>
       <c r="H492" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Atacama </t>
+          <t>Atacama</t>
         </is>
       </c>
       <c r="I492" t="inlineStr">
@@ -30504,7 +30504,7 @@
       </c>
       <c r="H493" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de la Araucanía </t>
+          <t>Araucanía</t>
         </is>
       </c>
       <c r="I493" t="inlineStr">
@@ -30565,7 +30565,7 @@
       </c>
       <c r="H494" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de los Lagos </t>
+          <t>Los Lagos</t>
         </is>
       </c>
       <c r="I494" t="inlineStr">
@@ -30626,7 +30626,7 @@
       </c>
       <c r="H495" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de la Araucanía </t>
+          <t>Araucanía</t>
         </is>
       </c>
       <c r="I495" t="inlineStr">
@@ -30687,7 +30687,7 @@
       </c>
       <c r="H496" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Maule </t>
+          <t>Maule</t>
         </is>
       </c>
       <c r="I496" t="inlineStr">
@@ -30748,7 +30748,7 @@
       </c>
       <c r="H497" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I497" t="inlineStr">
@@ -30809,7 +30809,7 @@
       </c>
       <c r="H498" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I498" t="inlineStr">
@@ -30870,7 +30870,7 @@
       </c>
       <c r="H499" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I499" t="inlineStr">
@@ -30931,7 +30931,7 @@
       </c>
       <c r="H500" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de los Lagos </t>
+          <t>Los Lagos</t>
         </is>
       </c>
       <c r="I500" t="inlineStr">
@@ -30992,7 +30992,7 @@
       </c>
       <c r="H501" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Valparaíso </t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I501" t="inlineStr">
@@ -31053,7 +31053,7 @@
       </c>
       <c r="H502" t="inlineStr">
         <is>
-          <t>Región del Ñuble</t>
+          <t>Ñuble</t>
         </is>
       </c>
       <c r="I502" t="inlineStr">
@@ -31175,7 +31175,7 @@
       </c>
       <c r="H504" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I504" t="inlineStr">
@@ -31236,7 +31236,7 @@
       </c>
       <c r="H505" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Biobío </t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I505" t="inlineStr">
@@ -31297,7 +31297,7 @@
       </c>
       <c r="H506" t="inlineStr">
         <is>
-          <t>Región de Los Ríos</t>
+          <t>Los Ríos</t>
         </is>
       </c>
       <c r="I506" t="inlineStr">
@@ -31358,7 +31358,7 @@
       </c>
       <c r="H507" t="inlineStr">
         <is>
-          <t>Región de Los Ríos</t>
+          <t>Los Ríos</t>
         </is>
       </c>
       <c r="I507" t="inlineStr">
@@ -31419,7 +31419,7 @@
       </c>
       <c r="H508" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I508" t="inlineStr">
@@ -31480,7 +31480,7 @@
       </c>
       <c r="H509" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I509" t="inlineStr">
@@ -31541,7 +31541,7 @@
       </c>
       <c r="H510" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de los Lagos </t>
+          <t>Los Lagos</t>
         </is>
       </c>
       <c r="I510" t="inlineStr">
@@ -31602,7 +31602,7 @@
       </c>
       <c r="H511" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Biobío </t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I511" t="inlineStr">
@@ -31663,7 +31663,7 @@
       </c>
       <c r="H512" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I512" t="inlineStr">
@@ -31724,7 +31724,7 @@
       </c>
       <c r="H513" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I513" t="inlineStr">
@@ -31785,7 +31785,7 @@
       </c>
       <c r="H514" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Biobío </t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I514" t="inlineStr">
@@ -31846,7 +31846,7 @@
       </c>
       <c r="H515" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I515" t="inlineStr">
@@ -31907,7 +31907,7 @@
       </c>
       <c r="H516" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I516" t="inlineStr">
@@ -31968,7 +31968,7 @@
       </c>
       <c r="H517" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Coquimbo </t>
+          <t>Coquimbo</t>
         </is>
       </c>
       <c r="I517" t="inlineStr">
@@ -32029,7 +32029,7 @@
       </c>
       <c r="H518" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de los Lagos </t>
+          <t>Los Lagos</t>
         </is>
       </c>
       <c r="I518" t="inlineStr">
@@ -32151,7 +32151,7 @@
       </c>
       <c r="H520" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I520" t="inlineStr">
@@ -32166,7 +32166,7 @@
       </c>
       <c r="K520" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="L520" t="inlineStr">
@@ -32216,7 +32216,7 @@
       </c>
       <c r="H521" t="inlineStr">
         <is>
-          <t>Región del Libertador General Bernardo O´Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I521" t="inlineStr">
@@ -32277,7 +32277,7 @@
       </c>
       <c r="H522" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I522" t="inlineStr">
@@ -32338,7 +32338,7 @@
       </c>
       <c r="H523" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Coquimbo </t>
+          <t>Coquimbo</t>
         </is>
       </c>
       <c r="I523" t="inlineStr">
@@ -32399,7 +32399,7 @@
       </c>
       <c r="H524" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Valparaíso </t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I524" t="inlineStr">
@@ -32460,7 +32460,7 @@
       </c>
       <c r="H525" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Coquimbo </t>
+          <t>Coquimbo</t>
         </is>
       </c>
       <c r="I525" t="inlineStr">
@@ -32521,7 +32521,7 @@
       </c>
       <c r="H526" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Biobío </t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I526" t="inlineStr">
@@ -32582,7 +32582,7 @@
       </c>
       <c r="H527" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de la Araucanía </t>
+          <t>Araucanía</t>
         </is>
       </c>
       <c r="I527" t="inlineStr">
@@ -32643,7 +32643,7 @@
       </c>
       <c r="H528" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de la Araucanía </t>
+          <t>Araucanía</t>
         </is>
       </c>
       <c r="I528" t="inlineStr">
@@ -32704,7 +32704,7 @@
       </c>
       <c r="H529" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de los Lagos </t>
+          <t>Los Lagos</t>
         </is>
       </c>
       <c r="I529" t="inlineStr">
@@ -32765,7 +32765,7 @@
       </c>
       <c r="H530" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I530" t="inlineStr">
@@ -32826,7 +32826,7 @@
       </c>
       <c r="H531" t="inlineStr">
         <is>
-          <t>Región de Arica y Parinacota</t>
+          <t>Arica y Parinacota</t>
         </is>
       </c>
       <c r="I531" t="inlineStr">
@@ -32887,7 +32887,7 @@
       </c>
       <c r="H532" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I532" t="inlineStr">
@@ -32948,7 +32948,7 @@
       </c>
       <c r="H533" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I533" t="inlineStr">
@@ -33009,7 +33009,7 @@
       </c>
       <c r="H534" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de los Lagos </t>
+          <t>Los Lagos</t>
         </is>
       </c>
       <c r="I534" t="inlineStr">
@@ -33070,7 +33070,7 @@
       </c>
       <c r="H535" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Valparaíso </t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I535" t="inlineStr">
@@ -33131,7 +33131,7 @@
       </c>
       <c r="H536" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I536" t="inlineStr">
@@ -33192,7 +33192,7 @@
       </c>
       <c r="H537" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I537" t="inlineStr">
@@ -33253,7 +33253,7 @@
       </c>
       <c r="H538" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Maule </t>
+          <t>Maule</t>
         </is>
       </c>
       <c r="I538" t="inlineStr">
@@ -33314,7 +33314,7 @@
       </c>
       <c r="H539" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Atacama </t>
+          <t>Atacama</t>
         </is>
       </c>
       <c r="I539" t="inlineStr">
@@ -33375,7 +33375,7 @@
       </c>
       <c r="H540" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I540" t="inlineStr">
@@ -33497,7 +33497,7 @@
       </c>
       <c r="H542" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I542" t="inlineStr">
@@ -33558,7 +33558,7 @@
       </c>
       <c r="H543" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de la Araucanía </t>
+          <t>Araucanía</t>
         </is>
       </c>
       <c r="I543" t="inlineStr">
@@ -33619,7 +33619,7 @@
       </c>
       <c r="H544" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I544" t="inlineStr">
@@ -33680,7 +33680,7 @@
       </c>
       <c r="H545" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Atacama </t>
+          <t>Atacama</t>
         </is>
       </c>
       <c r="I545" t="inlineStr">
@@ -33741,7 +33741,7 @@
       </c>
       <c r="H546" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Biobío </t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I546" t="inlineStr">
@@ -33802,7 +33802,7 @@
       </c>
       <c r="H547" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Valparaíso </t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I547" t="inlineStr">
@@ -33863,7 +33863,7 @@
       </c>
       <c r="H548" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Valparaíso </t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I548" t="inlineStr">
@@ -33924,7 +33924,7 @@
       </c>
       <c r="H549" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de la Araucanía </t>
+          <t>Araucanía</t>
         </is>
       </c>
       <c r="I549" t="inlineStr">
@@ -33985,7 +33985,7 @@
       </c>
       <c r="H550" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Valparaíso </t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I550" t="inlineStr">
@@ -34046,7 +34046,7 @@
       </c>
       <c r="H551" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I551" t="inlineStr">
@@ -34107,7 +34107,7 @@
       </c>
       <c r="H552" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Valparaíso </t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I552" t="inlineStr">
@@ -34168,7 +34168,7 @@
       </c>
       <c r="H553" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Valparaíso </t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I553" t="inlineStr">
@@ -34229,7 +34229,7 @@
       </c>
       <c r="H554" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I554" t="inlineStr">
@@ -34290,7 +34290,7 @@
       </c>
       <c r="H555" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I555" t="inlineStr">
@@ -34351,7 +34351,7 @@
       </c>
       <c r="H556" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Biobío </t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I556" t="inlineStr">
@@ -34412,7 +34412,7 @@
       </c>
       <c r="H557" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de los Lagos </t>
+          <t>Los Lagos</t>
         </is>
       </c>
       <c r="I557" t="inlineStr">
@@ -34473,7 +34473,7 @@
       </c>
       <c r="H558" t="inlineStr">
         <is>
-          <t>Región Aysén del General Carlos Ibáñez del Campo</t>
+          <t>Aysén</t>
         </is>
       </c>
       <c r="I558" t="inlineStr">
@@ -34534,7 +34534,7 @@
       </c>
       <c r="H559" t="inlineStr">
         <is>
-          <t>Región de Arica y Parinacota</t>
+          <t>Arica y Parinacota</t>
         </is>
       </c>
       <c r="I559" t="inlineStr">
@@ -34595,7 +34595,7 @@
       </c>
       <c r="H560" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Biobío </t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I560" t="inlineStr">
@@ -34656,7 +34656,7 @@
       </c>
       <c r="H561" t="inlineStr">
         <is>
-          <t>Región de Los Ríos</t>
+          <t>Los Ríos</t>
         </is>
       </c>
       <c r="I561" t="inlineStr">
@@ -34778,7 +34778,7 @@
       </c>
       <c r="H563" t="inlineStr">
         <is>
-          <t>Región de Arica y Parinacota</t>
+          <t>Arica y Parinacota</t>
         </is>
       </c>
       <c r="I563" t="inlineStr">
@@ -34839,7 +34839,7 @@
       </c>
       <c r="H564" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I564" t="inlineStr">
@@ -34900,7 +34900,7 @@
       </c>
       <c r="H565" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Antofagasta </t>
+          <t>Antofagasta</t>
         </is>
       </c>
       <c r="I565" t="inlineStr">
@@ -34961,7 +34961,7 @@
       </c>
       <c r="H566" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I566" t="inlineStr">
@@ -35022,7 +35022,7 @@
       </c>
       <c r="H567" t="inlineStr">
         <is>
-          <t>Región de Arica y Parinacota</t>
+          <t>Arica y Parinacota</t>
         </is>
       </c>
       <c r="I567" t="inlineStr">
@@ -35083,7 +35083,7 @@
       </c>
       <c r="H568" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I568" t="inlineStr">
@@ -35205,7 +35205,7 @@
       </c>
       <c r="H570" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Antofagasta </t>
+          <t>Antofagasta</t>
         </is>
       </c>
       <c r="I570" t="inlineStr">
@@ -35266,7 +35266,7 @@
       </c>
       <c r="H571" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I571" t="inlineStr">
@@ -35327,7 +35327,7 @@
       </c>
       <c r="H572" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Valparaíso </t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I572" t="inlineStr">
@@ -35388,7 +35388,7 @@
       </c>
       <c r="H573" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I573" t="inlineStr">
@@ -35449,7 +35449,7 @@
       </c>
       <c r="H574" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Maule </t>
+          <t>Maule</t>
         </is>
       </c>
       <c r="I574" t="inlineStr">
@@ -35510,7 +35510,7 @@
       </c>
       <c r="H575" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I575" t="inlineStr">
@@ -35571,7 +35571,7 @@
       </c>
       <c r="H576" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Maule </t>
+          <t>Maule</t>
         </is>
       </c>
       <c r="I576" t="inlineStr">
@@ -35632,7 +35632,7 @@
       </c>
       <c r="H577" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Valparaíso </t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I577" t="inlineStr">
@@ -35693,7 +35693,7 @@
       </c>
       <c r="H578" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de los Lagos </t>
+          <t>Los Lagos</t>
         </is>
       </c>
       <c r="I578" t="inlineStr">
@@ -35754,7 +35754,7 @@
       </c>
       <c r="H579" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I579" t="inlineStr">
@@ -35815,7 +35815,7 @@
       </c>
       <c r="H580" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Coquimbo </t>
+          <t>Coquimbo</t>
         </is>
       </c>
       <c r="I580" t="inlineStr">
@@ -35876,7 +35876,7 @@
       </c>
       <c r="H581" t="inlineStr">
         <is>
-          <t>Región Aysén del General Carlos Ibáñez del Campo</t>
+          <t>Aysén</t>
         </is>
       </c>
       <c r="I581" t="inlineStr">
@@ -35937,7 +35937,7 @@
       </c>
       <c r="H582" t="inlineStr">
         <is>
-          <t>Región de Arica y Parinacota</t>
+          <t>Arica y Parinacota</t>
         </is>
       </c>
       <c r="I582" t="inlineStr">
@@ -35998,7 +35998,7 @@
       </c>
       <c r="H583" t="inlineStr">
         <is>
-          <t>Región Aysén del General Carlos Ibáñez del Campo</t>
+          <t>Aysén</t>
         </is>
       </c>
       <c r="I583" t="inlineStr">
@@ -36059,7 +36059,7 @@
       </c>
       <c r="H584" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de los Lagos </t>
+          <t>Los Lagos</t>
         </is>
       </c>
       <c r="I584" t="inlineStr">
@@ -36120,7 +36120,7 @@
       </c>
       <c r="H585" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de la Araucanía </t>
+          <t>Araucanía</t>
         </is>
       </c>
       <c r="I585" t="inlineStr">
@@ -36242,7 +36242,7 @@
       </c>
       <c r="H587" t="inlineStr">
         <is>
-          <t>Región Aysén del General Carlos Ibáñez del Campo</t>
+          <t>Aysén</t>
         </is>
       </c>
       <c r="I587" t="inlineStr">
@@ -36303,7 +36303,7 @@
       </c>
       <c r="H588" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Valparaíso </t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I588" t="inlineStr">
@@ -36364,7 +36364,7 @@
       </c>
       <c r="H589" t="inlineStr">
         <is>
-          <t>Región del Ñuble</t>
+          <t>Ñuble</t>
         </is>
       </c>
       <c r="I589" t="inlineStr">
@@ -36425,7 +36425,7 @@
       </c>
       <c r="H590" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I590" t="inlineStr">
@@ -36486,7 +36486,7 @@
       </c>
       <c r="H591" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Coquimbo </t>
+          <t>Coquimbo</t>
         </is>
       </c>
       <c r="I591" t="inlineStr">
@@ -36547,7 +36547,7 @@
       </c>
       <c r="H592" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I592" t="inlineStr">
@@ -36608,7 +36608,7 @@
       </c>
       <c r="H593" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Biobío </t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I593" t="inlineStr">
@@ -36669,7 +36669,7 @@
       </c>
       <c r="H594" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Maule </t>
+          <t>Maule</t>
         </is>
       </c>
       <c r="I594" t="inlineStr">
@@ -36730,7 +36730,7 @@
       </c>
       <c r="H595" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de los Lagos </t>
+          <t>Los Lagos</t>
         </is>
       </c>
       <c r="I595" t="inlineStr">
@@ -36791,7 +36791,7 @@
       </c>
       <c r="H596" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I596" t="inlineStr">
@@ -36974,7 +36974,7 @@
       </c>
       <c r="H599" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Valparaíso </t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I599" t="inlineStr">
@@ -37096,7 +37096,7 @@
       </c>
       <c r="H601" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Valparaíso </t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I601" t="inlineStr">
@@ -37157,7 +37157,7 @@
       </c>
       <c r="H602" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Atacama </t>
+          <t>Atacama</t>
         </is>
       </c>
       <c r="I602" t="inlineStr">
@@ -37218,7 +37218,7 @@
       </c>
       <c r="H603" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de los Lagos </t>
+          <t>Los Lagos</t>
         </is>
       </c>
       <c r="I603" t="inlineStr">
@@ -37279,7 +37279,7 @@
       </c>
       <c r="H604" t="inlineStr">
         <is>
-          <t>Región de Los Ríos</t>
+          <t>Los Ríos</t>
         </is>
       </c>
       <c r="I604" t="inlineStr">
@@ -37340,7 +37340,7 @@
       </c>
       <c r="H605" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de los Lagos </t>
+          <t>Los Lagos</t>
         </is>
       </c>
       <c r="I605" t="inlineStr">
@@ -37401,7 +37401,7 @@
       </c>
       <c r="H606" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de los Lagos </t>
+          <t>Los Lagos</t>
         </is>
       </c>
       <c r="I606" t="inlineStr">
@@ -37462,7 +37462,7 @@
       </c>
       <c r="H607" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de los Lagos </t>
+          <t>Los Lagos</t>
         </is>
       </c>
       <c r="I607" t="inlineStr">
@@ -37523,7 +37523,7 @@
       </c>
       <c r="H608" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de la Araucanía </t>
+          <t>Araucanía</t>
         </is>
       </c>
       <c r="I608" t="inlineStr">
@@ -37584,7 +37584,7 @@
       </c>
       <c r="H609" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Valparaíso </t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I609" t="inlineStr">
@@ -37645,7 +37645,7 @@
       </c>
       <c r="H610" t="inlineStr">
         <is>
-          <t>Región del Ñuble</t>
+          <t>Ñuble</t>
         </is>
       </c>
       <c r="I610" t="inlineStr">
@@ -37706,7 +37706,7 @@
       </c>
       <c r="H611" t="inlineStr">
         <is>
-          <t>Región de Los Ríos</t>
+          <t>Los Ríos</t>
         </is>
       </c>
       <c r="I611" t="inlineStr">
@@ -37767,7 +37767,7 @@
       </c>
       <c r="H612" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I612" t="inlineStr">
@@ -37828,7 +37828,7 @@
       </c>
       <c r="H613" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Antofagasta </t>
+          <t>Antofagasta</t>
         </is>
       </c>
       <c r="I613" t="inlineStr">
@@ -37889,7 +37889,7 @@
       </c>
       <c r="H614" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Biobío </t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I614" t="inlineStr">
@@ -37950,7 +37950,7 @@
       </c>
       <c r="H615" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Coquimbo </t>
+          <t>Coquimbo</t>
         </is>
       </c>
       <c r="I615" t="inlineStr">
@@ -38011,7 +38011,7 @@
       </c>
       <c r="H616" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I616" t="inlineStr">
@@ -38072,7 +38072,7 @@
       </c>
       <c r="H617" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I617" t="inlineStr">
@@ -38133,7 +38133,7 @@
       </c>
       <c r="H618" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Maule </t>
+          <t>Maule</t>
         </is>
       </c>
       <c r="I618" t="inlineStr">
@@ -38194,7 +38194,7 @@
       </c>
       <c r="H619" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I619" t="inlineStr">
@@ -38255,7 +38255,7 @@
       </c>
       <c r="H620" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de los Lagos </t>
+          <t>Los Lagos</t>
         </is>
       </c>
       <c r="I620" t="inlineStr">
@@ -38316,7 +38316,7 @@
       </c>
       <c r="H621" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I621" t="inlineStr">
@@ -38377,7 +38377,7 @@
       </c>
       <c r="H622" t="inlineStr">
         <is>
-          <t>Región del Libertador General Bernardo O´Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I622" t="inlineStr">
@@ -38438,7 +38438,7 @@
       </c>
       <c r="H623" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I623" t="inlineStr">
@@ -38499,7 +38499,7 @@
       </c>
       <c r="H624" t="inlineStr">
         <is>
-          <t>Región del Libertador General Bernardo O´Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I624" t="inlineStr">
@@ -38560,7 +38560,7 @@
       </c>
       <c r="H625" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Antofagasta </t>
+          <t>Antofagasta</t>
         </is>
       </c>
       <c r="I625" t="inlineStr">
@@ -38621,7 +38621,7 @@
       </c>
       <c r="H626" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Coquimbo </t>
+          <t>Coquimbo</t>
         </is>
       </c>
       <c r="I626" t="inlineStr">
@@ -38682,7 +38682,7 @@
       </c>
       <c r="H627" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Biobío </t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I627" t="inlineStr">
@@ -38743,7 +38743,7 @@
       </c>
       <c r="H628" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de la Araucanía </t>
+          <t>Araucanía</t>
         </is>
       </c>
       <c r="I628" t="inlineStr">
@@ -38804,7 +38804,7 @@
       </c>
       <c r="H629" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Coquimbo </t>
+          <t>Coquimbo</t>
         </is>
       </c>
       <c r="I629" t="inlineStr">
@@ -38865,7 +38865,7 @@
       </c>
       <c r="H630" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Tarapacá  </t>
+          <t>Tarapacá</t>
         </is>
       </c>
       <c r="I630" t="inlineStr">
@@ -38926,7 +38926,7 @@
       </c>
       <c r="H631" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de los Lagos </t>
+          <t>Los Lagos</t>
         </is>
       </c>
       <c r="I631" t="inlineStr">
@@ -38987,7 +38987,7 @@
       </c>
       <c r="H632" t="inlineStr">
         <is>
-          <t>Región del Libertador General Bernardo O´Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I632" t="inlineStr">
@@ -39048,7 +39048,7 @@
       </c>
       <c r="H633" t="inlineStr">
         <is>
-          <t>Región del Libertador General Bernardo O´Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I633" t="inlineStr">
@@ -39109,7 +39109,7 @@
       </c>
       <c r="H634" t="inlineStr">
         <is>
-          <t>Región de Los Ríos</t>
+          <t>Los Ríos</t>
         </is>
       </c>
       <c r="I634" t="inlineStr">
@@ -39170,7 +39170,7 @@
       </c>
       <c r="H635" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de la Araucanía </t>
+          <t>Araucanía</t>
         </is>
       </c>
       <c r="I635" t="inlineStr">
@@ -39231,7 +39231,7 @@
       </c>
       <c r="H636" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Maule </t>
+          <t>Maule</t>
         </is>
       </c>
       <c r="I636" t="inlineStr">
@@ -39292,7 +39292,7 @@
       </c>
       <c r="H637" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de la Araucanía </t>
+          <t>Araucanía</t>
         </is>
       </c>
       <c r="I637" t="inlineStr">
@@ -39353,7 +39353,7 @@
       </c>
       <c r="H638" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I638" t="inlineStr">
@@ -39414,7 +39414,7 @@
       </c>
       <c r="H639" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Valparaíso </t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I639" t="inlineStr">
@@ -39475,7 +39475,7 @@
       </c>
       <c r="H640" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Antofagasta </t>
+          <t>Antofagasta</t>
         </is>
       </c>
       <c r="I640" t="inlineStr">
@@ -39597,7 +39597,7 @@
       </c>
       <c r="H642" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I642" t="inlineStr">
@@ -39719,7 +39719,7 @@
       </c>
       <c r="H644" t="inlineStr">
         <is>
-          <t>Región del Libertador General Bernardo O´Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I644" t="inlineStr">
@@ -39780,7 +39780,7 @@
       </c>
       <c r="H645" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de la Araucanía </t>
+          <t>Araucanía</t>
         </is>
       </c>
       <c r="I645" t="inlineStr">
@@ -39841,7 +39841,7 @@
       </c>
       <c r="H646" t="inlineStr">
         <is>
-          <t>Región del Ñuble</t>
+          <t>Ñuble</t>
         </is>
       </c>
       <c r="I646" t="inlineStr">
@@ -39902,7 +39902,7 @@
       </c>
       <c r="H647" t="inlineStr">
         <is>
-          <t>Región del Libertador General Bernardo O´Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I647" t="inlineStr">
@@ -39963,7 +39963,7 @@
       </c>
       <c r="H648" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I648" t="inlineStr">
@@ -40024,7 +40024,7 @@
       </c>
       <c r="H649" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Tarapacá  </t>
+          <t>Tarapacá</t>
         </is>
       </c>
       <c r="I649" t="inlineStr">
@@ -40085,7 +40085,7 @@
       </c>
       <c r="H650" t="inlineStr">
         <is>
-          <t>Región Aysén del General Carlos Ibáñez del Campo</t>
+          <t>Aysén</t>
         </is>
       </c>
       <c r="I650" t="inlineStr">
@@ -40146,7 +40146,7 @@
       </c>
       <c r="H651" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I651" t="inlineStr">
@@ -40268,7 +40268,7 @@
       </c>
       <c r="H653" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Coquimbo </t>
+          <t>Coquimbo</t>
         </is>
       </c>
       <c r="I653" t="inlineStr">
@@ -40329,7 +40329,7 @@
       </c>
       <c r="H654" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I654" t="inlineStr">
@@ -40390,7 +40390,7 @@
       </c>
       <c r="H655" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I655" t="inlineStr">
@@ -40451,7 +40451,7 @@
       </c>
       <c r="H656" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de los Lagos </t>
+          <t>Los Lagos</t>
         </is>
       </c>
       <c r="I656" t="inlineStr">
@@ -40512,7 +40512,7 @@
       </c>
       <c r="H657" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Biobío </t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I657" t="inlineStr">
@@ -40573,7 +40573,7 @@
       </c>
       <c r="H658" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I658" t="inlineStr">
@@ -40634,7 +40634,7 @@
       </c>
       <c r="H659" t="inlineStr">
         <is>
-          <t>Región del Libertador General Bernardo O´Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I659" t="inlineStr">
@@ -40695,7 +40695,7 @@
       </c>
       <c r="H660" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I660" t="inlineStr">
@@ -40756,7 +40756,7 @@
       </c>
       <c r="H661" t="inlineStr">
         <is>
-          <t>Región del Libertador General Bernardo O´Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I661" t="inlineStr">
@@ -40817,7 +40817,7 @@
       </c>
       <c r="H662" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Valparaíso </t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I662" t="inlineStr">
@@ -40939,7 +40939,7 @@
       </c>
       <c r="H664" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Antofagasta </t>
+          <t>Antofagasta</t>
         </is>
       </c>
       <c r="I664" t="inlineStr">
@@ -41000,7 +41000,7 @@
       </c>
       <c r="H665" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de los Lagos </t>
+          <t>Los Lagos</t>
         </is>
       </c>
       <c r="I665" t="inlineStr">
@@ -41061,7 +41061,7 @@
       </c>
       <c r="H666" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Biobío </t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I666" t="inlineStr">
@@ -41122,7 +41122,7 @@
       </c>
       <c r="H667" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I667" t="inlineStr">
@@ -41183,7 +41183,7 @@
       </c>
       <c r="H668" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Valparaíso </t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I668" t="inlineStr">
@@ -41244,7 +41244,7 @@
       </c>
       <c r="H669" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Valparaíso </t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I669" t="inlineStr">
@@ -41305,7 +41305,7 @@
       </c>
       <c r="H670" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I670" t="inlineStr">
@@ -41366,7 +41366,7 @@
       </c>
       <c r="H671" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de la Araucanía </t>
+          <t>Araucanía</t>
         </is>
       </c>
       <c r="I671" t="inlineStr">
@@ -41427,7 +41427,7 @@
       </c>
       <c r="H672" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I672" t="inlineStr">
@@ -41488,7 +41488,7 @@
       </c>
       <c r="H673" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Antofagasta </t>
+          <t>Antofagasta</t>
         </is>
       </c>
       <c r="I673" t="inlineStr">
@@ -41549,7 +41549,7 @@
       </c>
       <c r="H674" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Atacama </t>
+          <t>Atacama</t>
         </is>
       </c>
       <c r="I674" t="inlineStr">
@@ -41610,7 +41610,7 @@
       </c>
       <c r="H675" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Tarapacá  </t>
+          <t>Tarapacá</t>
         </is>
       </c>
       <c r="I675" t="inlineStr">
@@ -41671,7 +41671,7 @@
       </c>
       <c r="H676" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Biobío </t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I676" t="inlineStr">
@@ -41732,7 +41732,7 @@
       </c>
       <c r="H677" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de la Araucanía </t>
+          <t>Araucanía</t>
         </is>
       </c>
       <c r="I677" t="inlineStr">
@@ -41793,7 +41793,7 @@
       </c>
       <c r="H678" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I678" t="inlineStr">
@@ -41854,7 +41854,7 @@
       </c>
       <c r="H679" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I679" t="inlineStr">
@@ -41976,7 +41976,7 @@
       </c>
       <c r="H681" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I681" t="inlineStr">
@@ -42037,7 +42037,7 @@
       </c>
       <c r="H682" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Maule </t>
+          <t>Maule</t>
         </is>
       </c>
       <c r="I682" t="inlineStr">
@@ -42098,7 +42098,7 @@
       </c>
       <c r="H683" t="inlineStr">
         <is>
-          <t>Región del Ñuble</t>
+          <t>Ñuble</t>
         </is>
       </c>
       <c r="I683" t="inlineStr">
@@ -42159,7 +42159,7 @@
       </c>
       <c r="H684" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I684" t="inlineStr">
@@ -42220,7 +42220,7 @@
       </c>
       <c r="H685" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I685" t="inlineStr">
@@ -42281,7 +42281,7 @@
       </c>
       <c r="H686" t="inlineStr">
         <is>
-          <t>Región del Libertador General Bernardo O´Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I686" t="inlineStr">
@@ -42342,7 +42342,7 @@
       </c>
       <c r="H687" t="inlineStr">
         <is>
-          <t>Región del Libertador General Bernardo O´Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I687" t="inlineStr">
@@ -42403,7 +42403,7 @@
       </c>
       <c r="H688" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de la Araucanía </t>
+          <t>Araucanía</t>
         </is>
       </c>
       <c r="I688" t="inlineStr">
@@ -42464,7 +42464,7 @@
       </c>
       <c r="H689" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I689" t="inlineStr">
@@ -42525,7 +42525,7 @@
       </c>
       <c r="H690" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I690" t="inlineStr">
@@ -42586,7 +42586,7 @@
       </c>
       <c r="H691" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Maule </t>
+          <t>Maule</t>
         </is>
       </c>
       <c r="I691" t="inlineStr">
@@ -42647,7 +42647,7 @@
       </c>
       <c r="H692" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Valparaíso </t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I692" t="inlineStr">
@@ -42708,7 +42708,7 @@
       </c>
       <c r="H693" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I693" t="inlineStr">
@@ -42769,7 +42769,7 @@
       </c>
       <c r="H694" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I694" t="inlineStr">
@@ -42830,7 +42830,7 @@
       </c>
       <c r="H695" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de la Araucanía </t>
+          <t>Araucanía</t>
         </is>
       </c>
       <c r="I695" t="inlineStr">

--- a/docs/oc-mensuales/articulos-de-aseo-e-higiene/jun-2025.xlsx
+++ b/docs/oc-mensuales/articulos-de-aseo-e-higiene/jun-2025.xlsx
@@ -562,7 +562,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K2" t="inlineStr"/>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L2" t="inlineStr">
         <is>
           <t>USD</t>
@@ -623,7 +627,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K3" t="inlineStr"/>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L3" t="inlineStr">
         <is>
           <t>USD</t>
@@ -684,7 +692,11 @@
           <t>77.012.870-6</t>
         </is>
       </c>
-      <c r="K4" t="inlineStr"/>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>Coquimbo</t>
+        </is>
+      </c>
       <c r="L4" t="inlineStr">
         <is>
           <t>USD</t>
@@ -745,7 +757,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K5" t="inlineStr"/>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L5" t="inlineStr">
         <is>
           <t>USD</t>
@@ -867,7 +883,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K7" t="inlineStr"/>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L7" t="inlineStr">
         <is>
           <t>USD</t>
@@ -928,7 +948,11 @@
           <t>77.012.870-6</t>
         </is>
       </c>
-      <c r="K8" t="inlineStr"/>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>Coquimbo</t>
+        </is>
+      </c>
       <c r="L8" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1172,7 +1196,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K12" t="inlineStr"/>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L12" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1355,7 +1383,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K15" t="inlineStr"/>
+      <c r="K15" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L15" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1416,7 +1448,11 @@
           <t>78.906.980-8</t>
         </is>
       </c>
-      <c r="K16" t="inlineStr"/>
+      <c r="K16" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L16" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1477,7 +1513,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K17" t="inlineStr"/>
+      <c r="K17" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L17" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1599,7 +1639,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K19" t="inlineStr"/>
+      <c r="K19" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L19" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1782,7 +1826,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K22" t="inlineStr"/>
+      <c r="K22" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L22" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1965,7 +2013,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K25" t="inlineStr"/>
+      <c r="K25" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L25" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2026,7 +2078,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K26" t="inlineStr"/>
+      <c r="K26" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L26" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2087,7 +2143,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K27" t="inlineStr"/>
+      <c r="K27" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L27" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2148,7 +2208,11 @@
           <t>76.540.457-6</t>
         </is>
       </c>
-      <c r="K28" t="inlineStr"/>
+      <c r="K28" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L28" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2209,7 +2273,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K29" t="inlineStr"/>
+      <c r="K29" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L29" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2270,7 +2338,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K30" t="inlineStr"/>
+      <c r="K30" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L30" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2331,7 +2403,11 @@
           <t>77.621.112-5</t>
         </is>
       </c>
-      <c r="K31" t="inlineStr"/>
+      <c r="K31" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L31" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2392,7 +2468,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K32" t="inlineStr"/>
+      <c r="K32" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L32" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2636,7 +2716,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K36" t="inlineStr"/>
+      <c r="K36" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L36" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2880,7 +2964,11 @@
           <t>77.621.112-5</t>
         </is>
       </c>
-      <c r="K40" t="inlineStr"/>
+      <c r="K40" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L40" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2941,7 +3029,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K41" t="inlineStr"/>
+      <c r="K41" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L41" t="inlineStr">
         <is>
           <t>USD</t>
@@ -3185,7 +3277,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K45" t="inlineStr"/>
+      <c r="K45" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L45" t="inlineStr">
         <is>
           <t>USD</t>
@@ -3246,7 +3342,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K46" t="inlineStr"/>
+      <c r="K46" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L46" t="inlineStr">
         <is>
           <t>USD</t>
@@ -3307,7 +3407,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K47" t="inlineStr"/>
+      <c r="K47" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L47" t="inlineStr">
         <is>
           <t>USD</t>
@@ -3429,7 +3533,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K49" t="inlineStr"/>
+      <c r="K49" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L49" t="inlineStr">
         <is>
           <t>USD</t>
@@ -3673,7 +3781,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K53" t="inlineStr"/>
+      <c r="K53" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L53" t="inlineStr">
         <is>
           <t>USD</t>
@@ -3734,7 +3846,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K54" t="inlineStr"/>
+      <c r="K54" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L54" t="inlineStr">
         <is>
           <t>USD</t>
@@ -3856,7 +3972,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K56" t="inlineStr"/>
+      <c r="K56" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L56" t="inlineStr">
         <is>
           <t>USD</t>
@@ -3917,7 +4037,11 @@
           <t>76.299.358-9</t>
         </is>
       </c>
-      <c r="K57" t="inlineStr"/>
+      <c r="K57" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L57" t="inlineStr">
         <is>
           <t>USD</t>
@@ -3978,7 +4102,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K58" t="inlineStr"/>
+      <c r="K58" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L58" t="inlineStr">
         <is>
           <t>USD</t>
@@ -4039,7 +4167,11 @@
           <t>76.202.065-3</t>
         </is>
       </c>
-      <c r="K59" t="inlineStr"/>
+      <c r="K59" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L59" t="inlineStr">
         <is>
           <t>USD</t>
@@ -4100,7 +4232,11 @@
           <t>77.621.112-5</t>
         </is>
       </c>
-      <c r="K60" t="inlineStr"/>
+      <c r="K60" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L60" t="inlineStr">
         <is>
           <t>USD</t>
@@ -4222,7 +4358,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K62" t="inlineStr"/>
+      <c r="K62" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L62" t="inlineStr">
         <is>
           <t>USD</t>
@@ -4283,7 +4423,11 @@
           <t>76.540.457-6</t>
         </is>
       </c>
-      <c r="K63" t="inlineStr"/>
+      <c r="K63" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L63" t="inlineStr">
         <is>
           <t>USD</t>
@@ -4344,7 +4488,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K64" t="inlineStr"/>
+      <c r="K64" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L64" t="inlineStr">
         <is>
           <t>USD</t>
@@ -4405,7 +4553,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K65" t="inlineStr"/>
+      <c r="K65" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L65" t="inlineStr">
         <is>
           <t>USD</t>
@@ -4466,7 +4618,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K66" t="inlineStr"/>
+      <c r="K66" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L66" t="inlineStr">
         <is>
           <t>USD</t>
@@ -4527,7 +4683,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K67" t="inlineStr"/>
+      <c r="K67" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L67" t="inlineStr">
         <is>
           <t>USD</t>
@@ -4588,7 +4748,11 @@
           <t>76.905.483-9</t>
         </is>
       </c>
-      <c r="K68" t="inlineStr"/>
+      <c r="K68" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L68" t="inlineStr">
         <is>
           <t>USD</t>
@@ -4771,7 +4935,11 @@
           <t>89.842.300-k</t>
         </is>
       </c>
-      <c r="K71" t="inlineStr"/>
+      <c r="K71" t="inlineStr">
+        <is>
+          <t>Biobío</t>
+        </is>
+      </c>
       <c r="L71" t="inlineStr">
         <is>
           <t>USD</t>
@@ -4893,7 +5061,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K73" t="inlineStr"/>
+      <c r="K73" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L73" t="inlineStr">
         <is>
           <t>USD</t>
@@ -5076,7 +5248,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K76" t="inlineStr"/>
+      <c r="K76" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L76" t="inlineStr">
         <is>
           <t>USD</t>
@@ -5137,7 +5313,11 @@
           <t>76.202.065-3</t>
         </is>
       </c>
-      <c r="K77" t="inlineStr"/>
+      <c r="K77" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L77" t="inlineStr">
         <is>
           <t>USD</t>
@@ -5259,7 +5439,11 @@
           <t>77.610.393-4</t>
         </is>
       </c>
-      <c r="K79" t="inlineStr"/>
+      <c r="K79" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L79" t="inlineStr">
         <is>
           <t>USD</t>
@@ -5381,7 +5565,11 @@
           <t>76.540.457-6</t>
         </is>
       </c>
-      <c r="K81" t="inlineStr"/>
+      <c r="K81" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L81" t="inlineStr">
         <is>
           <t>USD</t>
@@ -5625,7 +5813,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K85" t="inlineStr"/>
+      <c r="K85" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L85" t="inlineStr">
         <is>
           <t>USD</t>
@@ -5747,7 +5939,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K87" t="inlineStr"/>
+      <c r="K87" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L87" t="inlineStr">
         <is>
           <t>USD</t>
@@ -5873,7 +6069,11 @@
           <t>78.906.980-8</t>
         </is>
       </c>
-      <c r="K89" t="inlineStr"/>
+      <c r="K89" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L89" t="inlineStr">
         <is>
           <t>USD</t>
@@ -6056,7 +6256,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K92" t="inlineStr"/>
+      <c r="K92" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L92" t="inlineStr">
         <is>
           <t>USD</t>
@@ -6117,7 +6321,11 @@
           <t>77.610.393-4</t>
         </is>
       </c>
-      <c r="K93" t="inlineStr"/>
+      <c r="K93" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L93" t="inlineStr">
         <is>
           <t>USD</t>
@@ -6178,7 +6386,11 @@
           <t>77.012.870-6</t>
         </is>
       </c>
-      <c r="K94" t="inlineStr"/>
+      <c r="K94" t="inlineStr">
+        <is>
+          <t>Coquimbo</t>
+        </is>
+      </c>
       <c r="L94" t="inlineStr">
         <is>
           <t>USD</t>
@@ -6239,7 +6451,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K95" t="inlineStr"/>
+      <c r="K95" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L95" t="inlineStr">
         <is>
           <t>USD</t>
@@ -6300,7 +6516,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K96" t="inlineStr"/>
+      <c r="K96" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L96" t="inlineStr">
         <is>
           <t>USD</t>
@@ -6422,7 +6642,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K98" t="inlineStr"/>
+      <c r="K98" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L98" t="inlineStr">
         <is>
           <t>USD</t>
@@ -6544,7 +6768,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K100" t="inlineStr"/>
+      <c r="K100" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L100" t="inlineStr">
         <is>
           <t>USD</t>
@@ -6605,7 +6833,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K101" t="inlineStr"/>
+      <c r="K101" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L101" t="inlineStr">
         <is>
           <t>USD</t>
@@ -6666,7 +6898,11 @@
           <t>78.906.980-8</t>
         </is>
       </c>
-      <c r="K102" t="inlineStr"/>
+      <c r="K102" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L102" t="inlineStr">
         <is>
           <t>USD</t>
@@ -6727,7 +6963,11 @@
           <t>77.012.870-6</t>
         </is>
       </c>
-      <c r="K103" t="inlineStr"/>
+      <c r="K103" t="inlineStr">
+        <is>
+          <t>Coquimbo</t>
+        </is>
+      </c>
       <c r="L103" t="inlineStr">
         <is>
           <t>USD</t>
@@ -6849,7 +7089,11 @@
           <t>78.906.980-8</t>
         </is>
       </c>
-      <c r="K105" t="inlineStr"/>
+      <c r="K105" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L105" t="inlineStr">
         <is>
           <t>USD</t>
@@ -6910,7 +7154,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K106" t="inlineStr"/>
+      <c r="K106" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L106" t="inlineStr">
         <is>
           <t>USD</t>
@@ -6971,7 +7219,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K107" t="inlineStr"/>
+      <c r="K107" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L107" t="inlineStr">
         <is>
           <t>USD</t>
@@ -7093,7 +7345,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K109" t="inlineStr"/>
+      <c r="K109" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L109" t="inlineStr">
         <is>
           <t>USD</t>
@@ -7154,7 +7410,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K110" t="inlineStr"/>
+      <c r="K110" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L110" t="inlineStr">
         <is>
           <t>USD</t>
@@ -7459,7 +7719,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K115" t="inlineStr"/>
+      <c r="K115" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L115" t="inlineStr">
         <is>
           <t>USD</t>
@@ -7520,7 +7784,11 @@
           <t>77.012.870-6</t>
         </is>
       </c>
-      <c r="K116" t="inlineStr"/>
+      <c r="K116" t="inlineStr">
+        <is>
+          <t>Coquimbo</t>
+        </is>
+      </c>
       <c r="L116" t="inlineStr">
         <is>
           <t>USD</t>
@@ -7703,7 +7971,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K119" t="inlineStr"/>
+      <c r="K119" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L119" t="inlineStr">
         <is>
           <t>USD</t>
@@ -7764,7 +8036,11 @@
           <t>77.610.393-4</t>
         </is>
       </c>
-      <c r="K120" t="inlineStr"/>
+      <c r="K120" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L120" t="inlineStr">
         <is>
           <t>USD</t>
@@ -8008,7 +8284,11 @@
           <t>76.202.065-3</t>
         </is>
       </c>
-      <c r="K124" t="inlineStr"/>
+      <c r="K124" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L124" t="inlineStr">
         <is>
           <t>USD</t>
@@ -8130,7 +8410,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K126" t="inlineStr"/>
+      <c r="K126" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L126" t="inlineStr">
         <is>
           <t>USD</t>
@@ -8191,7 +8475,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K127" t="inlineStr"/>
+      <c r="K127" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L127" t="inlineStr">
         <is>
           <t>USD</t>
@@ -8252,7 +8540,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K128" t="inlineStr"/>
+      <c r="K128" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L128" t="inlineStr">
         <is>
           <t>USD</t>
@@ -8435,7 +8727,11 @@
           <t>77.610.393-4</t>
         </is>
       </c>
-      <c r="K131" t="inlineStr"/>
+      <c r="K131" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L131" t="inlineStr">
         <is>
           <t>USD</t>
@@ -8496,7 +8792,11 @@
           <t>78.906.980-8</t>
         </is>
       </c>
-      <c r="K132" t="inlineStr"/>
+      <c r="K132" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L132" t="inlineStr">
         <is>
           <t>USD</t>
@@ -8618,7 +8918,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K134" t="inlineStr"/>
+      <c r="K134" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L134" t="inlineStr">
         <is>
           <t>USD</t>
@@ -8679,7 +8983,11 @@
           <t>76.540.457-6</t>
         </is>
       </c>
-      <c r="K135" t="inlineStr"/>
+      <c r="K135" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L135" t="inlineStr">
         <is>
           <t>USD</t>
@@ -8862,7 +9170,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K138" t="inlineStr"/>
+      <c r="K138" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L138" t="inlineStr">
         <is>
           <t>USD</t>
@@ -8923,7 +9235,11 @@
           <t>89.842.300-k</t>
         </is>
       </c>
-      <c r="K139" t="inlineStr"/>
+      <c r="K139" t="inlineStr">
+        <is>
+          <t>Biobío</t>
+        </is>
+      </c>
       <c r="L139" t="inlineStr">
         <is>
           <t>USD</t>
@@ -8984,7 +9300,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K140" t="inlineStr"/>
+      <c r="K140" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L140" t="inlineStr">
         <is>
           <t>USD</t>
@@ -9167,7 +9487,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K143" t="inlineStr"/>
+      <c r="K143" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L143" t="inlineStr">
         <is>
           <t>USD</t>
@@ -9289,7 +9613,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K145" t="inlineStr"/>
+      <c r="K145" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L145" t="inlineStr">
         <is>
           <t>USD</t>
@@ -9350,7 +9678,11 @@
           <t>77.082.051-0</t>
         </is>
       </c>
-      <c r="K146" t="inlineStr"/>
+      <c r="K146" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L146" t="inlineStr">
         <is>
           <t>USD</t>
@@ -9411,7 +9743,11 @@
           <t>78.307.990-9</t>
         </is>
       </c>
-      <c r="K147" t="inlineStr"/>
+      <c r="K147" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L147" t="inlineStr">
         <is>
           <t>USD</t>
@@ -9472,7 +9808,11 @@
           <t>77.012.870-6</t>
         </is>
       </c>
-      <c r="K148" t="inlineStr"/>
+      <c r="K148" t="inlineStr">
+        <is>
+          <t>Coquimbo</t>
+        </is>
+      </c>
       <c r="L148" t="inlineStr">
         <is>
           <t>USD</t>
@@ -9533,7 +9873,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K149" t="inlineStr"/>
+      <c r="K149" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L149" t="inlineStr">
         <is>
           <t>USD</t>
@@ -9594,7 +9938,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K150" t="inlineStr"/>
+      <c r="K150" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L150" t="inlineStr">
         <is>
           <t>USD</t>
@@ -9655,7 +10003,11 @@
           <t>89.842.300-k</t>
         </is>
       </c>
-      <c r="K151" t="inlineStr"/>
+      <c r="K151" t="inlineStr">
+        <is>
+          <t>Biobío</t>
+        </is>
+      </c>
       <c r="L151" t="inlineStr">
         <is>
           <t>USD</t>
@@ -9716,7 +10068,11 @@
           <t>78.906.980-8</t>
         </is>
       </c>
-      <c r="K152" t="inlineStr"/>
+      <c r="K152" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L152" t="inlineStr">
         <is>
           <t>USD</t>
@@ -9838,7 +10194,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K154" t="inlineStr"/>
+      <c r="K154" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L154" t="inlineStr">
         <is>
           <t>USD</t>
@@ -9899,7 +10259,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K155" t="inlineStr"/>
+      <c r="K155" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L155" t="inlineStr">
         <is>
           <t>USD</t>
@@ -9960,7 +10324,11 @@
           <t>78.906.980-8</t>
         </is>
       </c>
-      <c r="K156" t="inlineStr"/>
+      <c r="K156" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L156" t="inlineStr">
         <is>
           <t>USD</t>
@@ -10143,7 +10511,11 @@
           <t>78.906.980-8</t>
         </is>
       </c>
-      <c r="K159" t="inlineStr"/>
+      <c r="K159" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L159" t="inlineStr">
         <is>
           <t>USD</t>
@@ -10265,7 +10637,11 @@
           <t>76.202.065-3</t>
         </is>
       </c>
-      <c r="K161" t="inlineStr"/>
+      <c r="K161" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L161" t="inlineStr">
         <is>
           <t>USD</t>
@@ -10326,7 +10702,11 @@
           <t>76.540.457-6</t>
         </is>
       </c>
-      <c r="K162" t="inlineStr"/>
+      <c r="K162" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L162" t="inlineStr">
         <is>
           <t>USD</t>
@@ -10692,7 +11072,11 @@
           <t>76.202.065-3</t>
         </is>
       </c>
-      <c r="K168" t="inlineStr"/>
+      <c r="K168" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L168" t="inlineStr">
         <is>
           <t>USD</t>
@@ -10936,7 +11320,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K172" t="inlineStr"/>
+      <c r="K172" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L172" t="inlineStr">
         <is>
           <t>USD</t>
@@ -10997,7 +11385,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K173" t="inlineStr"/>
+      <c r="K173" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L173" t="inlineStr">
         <is>
           <t>USD</t>
@@ -11241,7 +11633,11 @@
           <t>78.307.990-9</t>
         </is>
       </c>
-      <c r="K177" t="inlineStr"/>
+      <c r="K177" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L177" t="inlineStr">
         <is>
           <t>USD</t>
@@ -11363,7 +11759,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K179" t="inlineStr"/>
+      <c r="K179" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L179" t="inlineStr">
         <is>
           <t>USD</t>
@@ -11607,7 +12007,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K183" t="inlineStr"/>
+      <c r="K183" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L183" t="inlineStr">
         <is>
           <t>USD</t>
@@ -11668,7 +12072,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K184" t="inlineStr"/>
+      <c r="K184" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L184" t="inlineStr">
         <is>
           <t>USD</t>
@@ -11851,7 +12259,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K187" t="inlineStr"/>
+      <c r="K187" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L187" t="inlineStr">
         <is>
           <t>USD</t>
@@ -11912,7 +12324,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K188" t="inlineStr"/>
+      <c r="K188" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L188" t="inlineStr">
         <is>
           <t>USD</t>
@@ -11973,7 +12389,11 @@
           <t>89.842.300-k</t>
         </is>
       </c>
-      <c r="K189" t="inlineStr"/>
+      <c r="K189" t="inlineStr">
+        <is>
+          <t>Biobío</t>
+        </is>
+      </c>
       <c r="L189" t="inlineStr">
         <is>
           <t>USD</t>
@@ -12034,7 +12454,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K190" t="inlineStr"/>
+      <c r="K190" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L190" t="inlineStr">
         <is>
           <t>USD</t>
@@ -12095,7 +12519,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K191" t="inlineStr"/>
+      <c r="K191" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L191" t="inlineStr">
         <is>
           <t>USD</t>
@@ -12156,7 +12584,11 @@
           <t>78.906.980-8</t>
         </is>
       </c>
-      <c r="K192" t="inlineStr"/>
+      <c r="K192" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L192" t="inlineStr">
         <is>
           <t>USD</t>
@@ -12217,7 +12649,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K193" t="inlineStr"/>
+      <c r="K193" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L193" t="inlineStr">
         <is>
           <t>USD</t>
@@ -12278,7 +12714,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K194" t="inlineStr"/>
+      <c r="K194" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L194" t="inlineStr">
         <is>
           <t>USD</t>
@@ -12339,7 +12779,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K195" t="inlineStr"/>
+      <c r="K195" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L195" t="inlineStr">
         <is>
           <t>USD</t>
@@ -12400,7 +12844,11 @@
           <t>76.299.358-9</t>
         </is>
       </c>
-      <c r="K196" t="inlineStr"/>
+      <c r="K196" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L196" t="inlineStr">
         <is>
           <t>USD</t>
@@ -12461,7 +12909,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K197" t="inlineStr"/>
+      <c r="K197" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L197" t="inlineStr">
         <is>
           <t>USD</t>
@@ -12522,7 +12974,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K198" t="inlineStr"/>
+      <c r="K198" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L198" t="inlineStr">
         <is>
           <t>USD</t>
@@ -12583,7 +13039,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K199" t="inlineStr"/>
+      <c r="K199" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L199" t="inlineStr">
         <is>
           <t>USD</t>
@@ -12705,7 +13165,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K201" t="inlineStr"/>
+      <c r="K201" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L201" t="inlineStr">
         <is>
           <t>USD</t>
@@ -12766,7 +13230,11 @@
           <t>76.540.457-6</t>
         </is>
       </c>
-      <c r="K202" t="inlineStr"/>
+      <c r="K202" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L202" t="inlineStr">
         <is>
           <t>USD</t>
@@ -12949,7 +13417,11 @@
           <t>76.299.358-9</t>
         </is>
       </c>
-      <c r="K205" t="inlineStr"/>
+      <c r="K205" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L205" t="inlineStr">
         <is>
           <t>USD</t>
@@ -13010,7 +13482,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K206" t="inlineStr"/>
+      <c r="K206" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L206" t="inlineStr">
         <is>
           <t>USD</t>
@@ -13071,7 +13547,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K207" t="inlineStr"/>
+      <c r="K207" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L207" t="inlineStr">
         <is>
           <t>USD</t>
@@ -13132,7 +13612,11 @@
           <t>77.012.870-6</t>
         </is>
       </c>
-      <c r="K208" t="inlineStr"/>
+      <c r="K208" t="inlineStr">
+        <is>
+          <t>Coquimbo</t>
+        </is>
+      </c>
       <c r="L208" t="inlineStr">
         <is>
           <t>USD</t>
@@ -13193,7 +13677,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K209" t="inlineStr"/>
+      <c r="K209" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L209" t="inlineStr">
         <is>
           <t>USD</t>
@@ -13315,7 +13803,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K211" t="inlineStr"/>
+      <c r="K211" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L211" t="inlineStr">
         <is>
           <t>USD</t>
@@ -13376,7 +13868,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K212" t="inlineStr"/>
+      <c r="K212" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L212" t="inlineStr">
         <is>
           <t>USD</t>
@@ -13559,7 +14055,11 @@
           <t>89.842.300-k</t>
         </is>
       </c>
-      <c r="K215" t="inlineStr"/>
+      <c r="K215" t="inlineStr">
+        <is>
+          <t>Biobío</t>
+        </is>
+      </c>
       <c r="L215" t="inlineStr">
         <is>
           <t>USD</t>
@@ -13620,7 +14120,11 @@
           <t>78.906.980-8</t>
         </is>
       </c>
-      <c r="K216" t="inlineStr"/>
+      <c r="K216" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L216" t="inlineStr">
         <is>
           <t>USD</t>
@@ -13681,7 +14185,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K217" t="inlineStr"/>
+      <c r="K217" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L217" t="inlineStr">
         <is>
           <t>USD</t>
@@ -13742,7 +14250,11 @@
           <t>76.540.457-6</t>
         </is>
       </c>
-      <c r="K218" t="inlineStr"/>
+      <c r="K218" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L218" t="inlineStr">
         <is>
           <t>USD</t>
@@ -13864,7 +14376,11 @@
           <t>78.906.980-8</t>
         </is>
       </c>
-      <c r="K220" t="inlineStr"/>
+      <c r="K220" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L220" t="inlineStr">
         <is>
           <t>USD</t>
@@ -13925,7 +14441,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K221" t="inlineStr"/>
+      <c r="K221" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L221" t="inlineStr">
         <is>
           <t>USD</t>
@@ -13986,7 +14506,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K222" t="inlineStr"/>
+      <c r="K222" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L222" t="inlineStr">
         <is>
           <t>USD</t>
@@ -14047,7 +14571,11 @@
           <t>77.623.039-1</t>
         </is>
       </c>
-      <c r="K223" t="inlineStr"/>
+      <c r="K223" t="inlineStr">
+        <is>
+          <t>Valparaíso</t>
+        </is>
+      </c>
       <c r="L223" t="inlineStr">
         <is>
           <t>USD</t>
@@ -14108,7 +14636,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K224" t="inlineStr"/>
+      <c r="K224" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L224" t="inlineStr">
         <is>
           <t>USD</t>
@@ -14169,7 +14701,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K225" t="inlineStr"/>
+      <c r="K225" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L225" t="inlineStr">
         <is>
           <t>USD</t>
@@ -14352,7 +14888,11 @@
           <t>76.100.933-8</t>
         </is>
       </c>
-      <c r="K228" t="inlineStr"/>
+      <c r="K228" t="inlineStr">
+        <is>
+          <t>Biobío</t>
+        </is>
+      </c>
       <c r="L228" t="inlineStr">
         <is>
           <t>USD</t>
@@ -14413,7 +14953,11 @@
           <t>76.540.457-6</t>
         </is>
       </c>
-      <c r="K229" t="inlineStr"/>
+      <c r="K229" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L229" t="inlineStr">
         <is>
           <t>USD</t>
@@ -14535,7 +15079,11 @@
           <t>78.906.980-8</t>
         </is>
       </c>
-      <c r="K231" t="inlineStr"/>
+      <c r="K231" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L231" t="inlineStr">
         <is>
           <t>USD</t>
@@ -14596,7 +15144,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K232" t="inlineStr"/>
+      <c r="K232" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L232" t="inlineStr">
         <is>
           <t>USD</t>
@@ -14657,7 +15209,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K233" t="inlineStr"/>
+      <c r="K233" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L233" t="inlineStr">
         <is>
           <t>USD</t>
@@ -14718,7 +15274,11 @@
           <t>8.306.984-8</t>
         </is>
       </c>
-      <c r="K234" t="inlineStr"/>
+      <c r="K234" t="inlineStr">
+        <is>
+          <t>Atacama</t>
+        </is>
+      </c>
       <c r="L234" t="inlineStr">
         <is>
           <t>USD</t>
@@ -14840,7 +15400,11 @@
           <t>78.906.980-8</t>
         </is>
       </c>
-      <c r="K236" t="inlineStr"/>
+      <c r="K236" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L236" t="inlineStr">
         <is>
           <t>USD</t>
@@ -14901,7 +15465,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K237" t="inlineStr"/>
+      <c r="K237" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L237" t="inlineStr">
         <is>
           <t>USD</t>
@@ -14962,7 +15530,11 @@
           <t>76.213.681-3</t>
         </is>
       </c>
-      <c r="K238" t="inlineStr"/>
+      <c r="K238" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L238" t="inlineStr">
         <is>
           <t>USD</t>
@@ -15023,7 +15595,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K239" t="inlineStr"/>
+      <c r="K239" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L239" t="inlineStr">
         <is>
           <t>USD</t>
@@ -15084,7 +15660,11 @@
           <t>89.842.300-k</t>
         </is>
       </c>
-      <c r="K240" t="inlineStr"/>
+      <c r="K240" t="inlineStr">
+        <is>
+          <t>Biobío</t>
+        </is>
+      </c>
       <c r="L240" t="inlineStr">
         <is>
           <t>USD</t>
@@ -15267,7 +15847,11 @@
           <t>77.012.870-6</t>
         </is>
       </c>
-      <c r="K243" t="inlineStr"/>
+      <c r="K243" t="inlineStr">
+        <is>
+          <t>Coquimbo</t>
+        </is>
+      </c>
       <c r="L243" t="inlineStr">
         <is>
           <t>USD</t>
@@ -15328,7 +15912,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K244" t="inlineStr"/>
+      <c r="K244" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L244" t="inlineStr">
         <is>
           <t>USD</t>
@@ -15389,7 +15977,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K245" t="inlineStr"/>
+      <c r="K245" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L245" t="inlineStr">
         <is>
           <t>USD</t>
@@ -15572,7 +16164,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K248" t="inlineStr"/>
+      <c r="K248" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L248" t="inlineStr">
         <is>
           <t>USD</t>
@@ -15633,7 +16229,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K249" t="inlineStr"/>
+      <c r="K249" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L249" t="inlineStr">
         <is>
           <t>USD</t>
@@ -15755,7 +16355,11 @@
           <t>89.842.300-k</t>
         </is>
       </c>
-      <c r="K251" t="inlineStr"/>
+      <c r="K251" t="inlineStr">
+        <is>
+          <t>Biobío</t>
+        </is>
+      </c>
       <c r="L251" t="inlineStr">
         <is>
           <t>USD</t>
@@ -15816,7 +16420,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K252" t="inlineStr"/>
+      <c r="K252" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L252" t="inlineStr">
         <is>
           <t>USD</t>
@@ -15877,7 +16485,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K253" t="inlineStr"/>
+      <c r="K253" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L253" t="inlineStr">
         <is>
           <t>USD</t>
@@ -15938,7 +16550,11 @@
           <t>76.202.065-3</t>
         </is>
       </c>
-      <c r="K254" t="inlineStr"/>
+      <c r="K254" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L254" t="inlineStr">
         <is>
           <t>USD</t>
@@ -15999,7 +16615,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K255" t="inlineStr"/>
+      <c r="K255" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L255" t="inlineStr">
         <is>
           <t>USD</t>
@@ -16060,7 +16680,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K256" t="inlineStr"/>
+      <c r="K256" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L256" t="inlineStr">
         <is>
           <t>USD</t>
@@ -16182,7 +16806,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K258" t="inlineStr"/>
+      <c r="K258" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L258" t="inlineStr">
         <is>
           <t>USD</t>
@@ -16304,7 +16932,11 @@
           <t>76.202.065-3</t>
         </is>
       </c>
-      <c r="K260" t="inlineStr"/>
+      <c r="K260" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L260" t="inlineStr">
         <is>
           <t>USD</t>
@@ -16487,7 +17119,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K263" t="inlineStr"/>
+      <c r="K263" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L263" t="inlineStr">
         <is>
           <t>USD</t>
@@ -16609,7 +17245,11 @@
           <t>77.621.112-5</t>
         </is>
       </c>
-      <c r="K265" t="inlineStr"/>
+      <c r="K265" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L265" t="inlineStr">
         <is>
           <t>USD</t>
@@ -16731,7 +17371,11 @@
           <t>78.906.980-8</t>
         </is>
       </c>
-      <c r="K267" t="inlineStr"/>
+      <c r="K267" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L267" t="inlineStr">
         <is>
           <t>USD</t>
@@ -16853,7 +17497,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K269" t="inlineStr"/>
+      <c r="K269" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L269" t="inlineStr">
         <is>
           <t>USD</t>
@@ -16975,7 +17623,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K271" t="inlineStr"/>
+      <c r="K271" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L271" t="inlineStr">
         <is>
           <t>USD</t>
@@ -17036,7 +17688,11 @@
           <t>89.842.300-k</t>
         </is>
       </c>
-      <c r="K272" t="inlineStr"/>
+      <c r="K272" t="inlineStr">
+        <is>
+          <t>Biobío</t>
+        </is>
+      </c>
       <c r="L272" t="inlineStr">
         <is>
           <t>USD</t>
@@ -17097,7 +17753,11 @@
           <t>89.842.300-k</t>
         </is>
       </c>
-      <c r="K273" t="inlineStr"/>
+      <c r="K273" t="inlineStr">
+        <is>
+          <t>Biobío</t>
+        </is>
+      </c>
       <c r="L273" t="inlineStr">
         <is>
           <t>USD</t>
@@ -17219,7 +17879,11 @@
           <t>78.906.980-8</t>
         </is>
       </c>
-      <c r="K275" t="inlineStr"/>
+      <c r="K275" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L275" t="inlineStr">
         <is>
           <t>USD</t>
@@ -17280,7 +17944,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K276" t="inlineStr"/>
+      <c r="K276" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L276" t="inlineStr">
         <is>
           <t>USD</t>
@@ -17341,7 +18009,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K277" t="inlineStr"/>
+      <c r="K277" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L277" t="inlineStr">
         <is>
           <t>USD</t>
@@ -17463,7 +18135,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K279" t="inlineStr"/>
+      <c r="K279" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L279" t="inlineStr">
         <is>
           <t>USD</t>
@@ -17585,7 +18261,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K281" t="inlineStr"/>
+      <c r="K281" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L281" t="inlineStr">
         <is>
           <t>USD</t>
@@ -17646,7 +18326,11 @@
           <t>77.610.393-4</t>
         </is>
       </c>
-      <c r="K282" t="inlineStr"/>
+      <c r="K282" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L282" t="inlineStr">
         <is>
           <t>USD</t>
@@ -17707,7 +18391,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K283" t="inlineStr"/>
+      <c r="K283" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L283" t="inlineStr">
         <is>
           <t>USD</t>
@@ -17829,7 +18517,11 @@
           <t>8.306.984-8</t>
         </is>
       </c>
-      <c r="K285" t="inlineStr"/>
+      <c r="K285" t="inlineStr">
+        <is>
+          <t>Atacama</t>
+        </is>
+      </c>
       <c r="L285" t="inlineStr">
         <is>
           <t>USD</t>
@@ -17951,7 +18643,11 @@
           <t>76.540.457-6</t>
         </is>
       </c>
-      <c r="K287" t="inlineStr"/>
+      <c r="K287" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L287" t="inlineStr">
         <is>
           <t>USD</t>
@@ -18073,7 +18769,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K289" t="inlineStr"/>
+      <c r="K289" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L289" t="inlineStr">
         <is>
           <t>USD</t>
@@ -18134,7 +18834,11 @@
           <t>78.906.980-8</t>
         </is>
       </c>
-      <c r="K290" t="inlineStr"/>
+      <c r="K290" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L290" t="inlineStr">
         <is>
           <t>USD</t>
@@ -18195,7 +18899,11 @@
           <t>77.012.870-6</t>
         </is>
       </c>
-      <c r="K291" t="inlineStr"/>
+      <c r="K291" t="inlineStr">
+        <is>
+          <t>Coquimbo</t>
+        </is>
+      </c>
       <c r="L291" t="inlineStr">
         <is>
           <t>USD</t>
@@ -18256,7 +18964,11 @@
           <t>76.202.065-3</t>
         </is>
       </c>
-      <c r="K292" t="inlineStr"/>
+      <c r="K292" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L292" t="inlineStr">
         <is>
           <t>USD</t>
@@ -18317,7 +19029,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K293" t="inlineStr"/>
+      <c r="K293" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L293" t="inlineStr">
         <is>
           <t>USD</t>
@@ -18378,7 +19094,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K294" t="inlineStr"/>
+      <c r="K294" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L294" t="inlineStr">
         <is>
           <t>USD</t>
@@ -18439,7 +19159,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K295" t="inlineStr"/>
+      <c r="K295" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L295" t="inlineStr">
         <is>
           <t>USD</t>
@@ -18500,7 +19224,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K296" t="inlineStr"/>
+      <c r="K296" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L296" t="inlineStr">
         <is>
           <t>USD</t>
@@ -18622,7 +19350,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K298" t="inlineStr"/>
+      <c r="K298" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L298" t="inlineStr">
         <is>
           <t>USD</t>
@@ -18683,7 +19415,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K299" t="inlineStr"/>
+      <c r="K299" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L299" t="inlineStr">
         <is>
           <t>USD</t>
@@ -18744,7 +19480,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K300" t="inlineStr"/>
+      <c r="K300" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L300" t="inlineStr">
         <is>
           <t>USD</t>
@@ -18805,7 +19545,11 @@
           <t>78.906.980-8</t>
         </is>
       </c>
-      <c r="K301" t="inlineStr"/>
+      <c r="K301" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L301" t="inlineStr">
         <is>
           <t>USD</t>
@@ -18866,7 +19610,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K302" t="inlineStr"/>
+      <c r="K302" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L302" t="inlineStr">
         <is>
           <t>USD</t>
@@ -18927,7 +19675,11 @@
           <t>76.540.457-6</t>
         </is>
       </c>
-      <c r="K303" t="inlineStr"/>
+      <c r="K303" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L303" t="inlineStr">
         <is>
           <t>USD</t>
@@ -18988,7 +19740,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K304" t="inlineStr"/>
+      <c r="K304" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L304" t="inlineStr">
         <is>
           <t>USD</t>
@@ -19110,7 +19866,11 @@
           <t>77.610.393-4</t>
         </is>
       </c>
-      <c r="K306" t="inlineStr"/>
+      <c r="K306" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L306" t="inlineStr">
         <is>
           <t>USD</t>
@@ -19171,7 +19931,11 @@
           <t>77.012.870-6</t>
         </is>
       </c>
-      <c r="K307" t="inlineStr"/>
+      <c r="K307" t="inlineStr">
+        <is>
+          <t>Coquimbo</t>
+        </is>
+      </c>
       <c r="L307" t="inlineStr">
         <is>
           <t>USD</t>
@@ -19293,7 +20057,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K309" t="inlineStr"/>
+      <c r="K309" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L309" t="inlineStr">
         <is>
           <t>USD</t>
@@ -19354,7 +20122,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K310" t="inlineStr"/>
+      <c r="K310" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L310" t="inlineStr">
         <is>
           <t>USD</t>
@@ -19537,7 +20309,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K313" t="inlineStr"/>
+      <c r="K313" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L313" t="inlineStr">
         <is>
           <t>USD</t>
@@ -19598,7 +20374,11 @@
           <t>79.722.860-5</t>
         </is>
       </c>
-      <c r="K314" t="inlineStr"/>
+      <c r="K314" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L314" t="inlineStr">
         <is>
           <t>USD</t>
@@ -19781,7 +20561,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K317" t="inlineStr"/>
+      <c r="K317" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L317" t="inlineStr">
         <is>
           <t>USD</t>
@@ -19903,7 +20687,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K319" t="inlineStr"/>
+      <c r="K319" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L319" t="inlineStr">
         <is>
           <t>USD</t>
@@ -19964,7 +20752,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K320" t="inlineStr"/>
+      <c r="K320" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L320" t="inlineStr">
         <is>
           <t>USD</t>
@@ -20025,7 +20817,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K321" t="inlineStr"/>
+      <c r="K321" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L321" t="inlineStr">
         <is>
           <t>USD</t>
@@ -20086,7 +20882,11 @@
           <t>76.202.065-3</t>
         </is>
       </c>
-      <c r="K322" t="inlineStr"/>
+      <c r="K322" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L322" t="inlineStr">
         <is>
           <t>USD</t>
@@ -20147,7 +20947,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K323" t="inlineStr"/>
+      <c r="K323" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L323" t="inlineStr">
         <is>
           <t>USD</t>
@@ -20330,7 +21134,11 @@
           <t>76.202.065-3</t>
         </is>
       </c>
-      <c r="K326" t="inlineStr"/>
+      <c r="K326" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L326" t="inlineStr">
         <is>
           <t>USD</t>
@@ -20391,7 +21199,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K327" t="inlineStr"/>
+      <c r="K327" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L327" t="inlineStr">
         <is>
           <t>USD</t>
@@ -20635,7 +21447,11 @@
           <t>77.053.654-5</t>
         </is>
       </c>
-      <c r="K331" t="inlineStr"/>
+      <c r="K331" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L331" t="inlineStr">
         <is>
           <t>USD</t>
@@ -20696,7 +21512,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K332" t="inlineStr"/>
+      <c r="K332" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L332" t="inlineStr">
         <is>
           <t>USD</t>
@@ -20757,7 +21577,11 @@
           <t>77.619.564-2</t>
         </is>
       </c>
-      <c r="K333" t="inlineStr"/>
+      <c r="K333" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L333" t="inlineStr">
         <is>
           <t>USD</t>
@@ -20818,7 +21642,11 @@
           <t>89.842.300-k</t>
         </is>
       </c>
-      <c r="K334" t="inlineStr"/>
+      <c r="K334" t="inlineStr">
+        <is>
+          <t>Biobío</t>
+        </is>
+      </c>
       <c r="L334" t="inlineStr">
         <is>
           <t>USD</t>
@@ -20879,7 +21707,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K335" t="inlineStr"/>
+      <c r="K335" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L335" t="inlineStr">
         <is>
           <t>USD</t>
@@ -20940,7 +21772,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K336" t="inlineStr"/>
+      <c r="K336" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L336" t="inlineStr">
         <is>
           <t>USD</t>
@@ -21062,7 +21898,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K338" t="inlineStr"/>
+      <c r="K338" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L338" t="inlineStr">
         <is>
           <t>USD</t>
@@ -21123,7 +21963,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K339" t="inlineStr"/>
+      <c r="K339" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L339" t="inlineStr">
         <is>
           <t>USD</t>
@@ -21306,7 +22150,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K342" t="inlineStr"/>
+      <c r="K342" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L342" t="inlineStr">
         <is>
           <t>USD</t>
@@ -21367,7 +22215,11 @@
           <t>77.621.112-5</t>
         </is>
       </c>
-      <c r="K343" t="inlineStr"/>
+      <c r="K343" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L343" t="inlineStr">
         <is>
           <t>USD</t>
@@ -21489,7 +22341,11 @@
           <t>76.299.358-9</t>
         </is>
       </c>
-      <c r="K345" t="inlineStr"/>
+      <c r="K345" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L345" t="inlineStr">
         <is>
           <t>USD</t>
@@ -21611,7 +22467,11 @@
           <t>8.306.984-8</t>
         </is>
       </c>
-      <c r="K347" t="inlineStr"/>
+      <c r="K347" t="inlineStr">
+        <is>
+          <t>Atacama</t>
+        </is>
+      </c>
       <c r="L347" t="inlineStr">
         <is>
           <t>USD</t>
@@ -21733,7 +22593,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K349" t="inlineStr"/>
+      <c r="K349" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L349" t="inlineStr">
         <is>
           <t>USD</t>
@@ -21794,7 +22658,11 @@
           <t>76.202.065-3</t>
         </is>
       </c>
-      <c r="K350" t="inlineStr"/>
+      <c r="K350" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L350" t="inlineStr">
         <is>
           <t>USD</t>
@@ -21916,7 +22784,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K352" t="inlineStr"/>
+      <c r="K352" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L352" t="inlineStr">
         <is>
           <t>USD</t>
@@ -22160,7 +23032,11 @@
           <t>77.012.870-6</t>
         </is>
       </c>
-      <c r="K356" t="inlineStr"/>
+      <c r="K356" t="inlineStr">
+        <is>
+          <t>Coquimbo</t>
+        </is>
+      </c>
       <c r="L356" t="inlineStr">
         <is>
           <t>USD</t>
@@ -22282,7 +23158,11 @@
           <t>76.202.065-3</t>
         </is>
       </c>
-      <c r="K358" t="inlineStr"/>
+      <c r="K358" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L358" t="inlineStr">
         <is>
           <t>USD</t>
@@ -22343,7 +23223,11 @@
           <t>78.906.980-8</t>
         </is>
       </c>
-      <c r="K359" t="inlineStr"/>
+      <c r="K359" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L359" t="inlineStr">
         <is>
           <t>USD</t>
@@ -22465,7 +23349,11 @@
           <t>77.610.393-4</t>
         </is>
       </c>
-      <c r="K361" t="inlineStr"/>
+      <c r="K361" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L361" t="inlineStr">
         <is>
           <t>USD</t>
@@ -22526,7 +23414,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K362" t="inlineStr"/>
+      <c r="K362" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L362" t="inlineStr">
         <is>
           <t>USD</t>
@@ -22587,7 +23479,11 @@
           <t>77.621.112-5</t>
         </is>
       </c>
-      <c r="K363" t="inlineStr"/>
+      <c r="K363" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L363" t="inlineStr">
         <is>
           <t>USD</t>
@@ -22709,7 +23605,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K365" t="inlineStr"/>
+      <c r="K365" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L365" t="inlineStr">
         <is>
           <t>USD</t>
@@ -22953,7 +23853,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K369" t="inlineStr"/>
+      <c r="K369" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L369" t="inlineStr">
         <is>
           <t>USD</t>
@@ -23014,7 +23918,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K370" t="inlineStr"/>
+      <c r="K370" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L370" t="inlineStr">
         <is>
           <t>USD</t>
@@ -23075,7 +23983,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K371" t="inlineStr"/>
+      <c r="K371" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L371" t="inlineStr">
         <is>
           <t>USD</t>
@@ -23136,7 +24048,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K372" t="inlineStr"/>
+      <c r="K372" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L372" t="inlineStr">
         <is>
           <t>USD</t>
@@ -23319,7 +24235,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K375" t="inlineStr"/>
+      <c r="K375" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L375" t="inlineStr">
         <is>
           <t>USD</t>
@@ -23502,7 +24422,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K378" t="inlineStr"/>
+      <c r="K378" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L378" t="inlineStr">
         <is>
           <t>USD</t>
@@ -23563,7 +24487,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K379" t="inlineStr"/>
+      <c r="K379" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L379" t="inlineStr">
         <is>
           <t>USD</t>
@@ -23624,7 +24552,11 @@
           <t>76.540.457-6</t>
         </is>
       </c>
-      <c r="K380" t="inlineStr"/>
+      <c r="K380" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L380" t="inlineStr">
         <is>
           <t>USD</t>
@@ -23685,7 +24617,11 @@
           <t>76.202.065-3</t>
         </is>
       </c>
-      <c r="K381" t="inlineStr"/>
+      <c r="K381" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L381" t="inlineStr">
         <is>
           <t>USD</t>
@@ -23807,7 +24743,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K383" t="inlineStr"/>
+      <c r="K383" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L383" t="inlineStr">
         <is>
           <t>USD</t>
@@ -23990,7 +24930,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K386" t="inlineStr"/>
+      <c r="K386" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L386" t="inlineStr">
         <is>
           <t>USD</t>
@@ -24051,7 +24995,11 @@
           <t>78.906.980-8</t>
         </is>
       </c>
-      <c r="K387" t="inlineStr"/>
+      <c r="K387" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L387" t="inlineStr">
         <is>
           <t>USD</t>
@@ -24356,7 +25304,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K392" t="inlineStr"/>
+      <c r="K392" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L392" t="inlineStr">
         <is>
           <t>USD</t>
@@ -24661,7 +25613,11 @@
           <t>77.053.654-5</t>
         </is>
       </c>
-      <c r="K397" t="inlineStr"/>
+      <c r="K397" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L397" t="inlineStr">
         <is>
           <t>USD</t>
@@ -24844,7 +25800,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K400" t="inlineStr"/>
+      <c r="K400" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L400" t="inlineStr">
         <is>
           <t>USD</t>
@@ -24905,7 +25865,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K401" t="inlineStr"/>
+      <c r="K401" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L401" t="inlineStr">
         <is>
           <t>USD</t>
@@ -25088,7 +26052,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K404" t="inlineStr"/>
+      <c r="K404" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L404" t="inlineStr">
         <is>
           <t>USD</t>
@@ -25210,7 +26178,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K406" t="inlineStr"/>
+      <c r="K406" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L406" t="inlineStr">
         <is>
           <t>USD</t>
@@ -25393,7 +26365,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K409" t="inlineStr"/>
+      <c r="K409" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L409" t="inlineStr">
         <is>
           <t>USD</t>
@@ -25515,7 +26491,11 @@
           <t>77.012.870-6</t>
         </is>
       </c>
-      <c r="K411" t="inlineStr"/>
+      <c r="K411" t="inlineStr">
+        <is>
+          <t>Coquimbo</t>
+        </is>
+      </c>
       <c r="L411" t="inlineStr">
         <is>
           <t>USD</t>
@@ -25637,7 +26617,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K413" t="inlineStr"/>
+      <c r="K413" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L413" t="inlineStr">
         <is>
           <t>USD</t>
@@ -25759,7 +26743,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K415" t="inlineStr"/>
+      <c r="K415" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L415" t="inlineStr">
         <is>
           <t>USD</t>
@@ -26003,7 +26991,11 @@
           <t>78.906.980-8</t>
         </is>
       </c>
-      <c r="K419" t="inlineStr"/>
+      <c r="K419" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L419" t="inlineStr">
         <is>
           <t>USD</t>
@@ -26186,7 +27178,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K422" t="inlineStr"/>
+      <c r="K422" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L422" t="inlineStr">
         <is>
           <t>USD</t>
@@ -26247,7 +27243,11 @@
           <t>76.540.457-6</t>
         </is>
       </c>
-      <c r="K423" t="inlineStr"/>
+      <c r="K423" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L423" t="inlineStr">
         <is>
           <t>USD</t>
@@ -26369,7 +27369,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K425" t="inlineStr"/>
+      <c r="K425" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L425" t="inlineStr">
         <is>
           <t>USD</t>
@@ -26491,7 +27495,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K427" t="inlineStr"/>
+      <c r="K427" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L427" t="inlineStr">
         <is>
           <t>USD</t>
@@ -26552,7 +27560,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K428" t="inlineStr"/>
+      <c r="K428" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L428" t="inlineStr">
         <is>
           <t>USD</t>
@@ -26735,7 +27747,11 @@
           <t>78.906.980-8</t>
         </is>
       </c>
-      <c r="K431" t="inlineStr"/>
+      <c r="K431" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L431" t="inlineStr">
         <is>
           <t>USD</t>
@@ -26796,7 +27812,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K432" t="inlineStr"/>
+      <c r="K432" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L432" t="inlineStr">
         <is>
           <t>USD</t>
@@ -26857,7 +27877,11 @@
           <t>78.307.990-9</t>
         </is>
       </c>
-      <c r="K433" t="inlineStr"/>
+      <c r="K433" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L433" t="inlineStr">
         <is>
           <t>USD</t>
@@ -27040,7 +28064,11 @@
           <t>76.202.065-3</t>
         </is>
       </c>
-      <c r="K436" t="inlineStr"/>
+      <c r="K436" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L436" t="inlineStr">
         <is>
           <t>USD</t>
@@ -27101,7 +28129,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K437" t="inlineStr"/>
+      <c r="K437" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L437" t="inlineStr">
         <is>
           <t>USD</t>
@@ -27162,7 +28194,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K438" t="inlineStr"/>
+      <c r="K438" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L438" t="inlineStr">
         <is>
           <t>USD</t>
@@ -27223,7 +28259,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K439" t="inlineStr"/>
+      <c r="K439" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L439" t="inlineStr">
         <is>
           <t>USD</t>
@@ -27284,7 +28324,11 @@
           <t>76.202.065-3</t>
         </is>
       </c>
-      <c r="K440" t="inlineStr"/>
+      <c r="K440" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L440" t="inlineStr">
         <is>
           <t>USD</t>
@@ -27406,7 +28450,11 @@
           <t>76.202.065-3</t>
         </is>
       </c>
-      <c r="K442" t="inlineStr"/>
+      <c r="K442" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L442" t="inlineStr">
         <is>
           <t>USD</t>
@@ -27528,7 +28576,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K444" t="inlineStr"/>
+      <c r="K444" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L444" t="inlineStr">
         <is>
           <t>USD</t>
@@ -27589,7 +28641,11 @@
           <t>76.299.358-9</t>
         </is>
       </c>
-      <c r="K445" t="inlineStr"/>
+      <c r="K445" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L445" t="inlineStr">
         <is>
           <t>USD</t>
@@ -27894,7 +28950,11 @@
           <t>76.540.457-6</t>
         </is>
       </c>
-      <c r="K450" t="inlineStr"/>
+      <c r="K450" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L450" t="inlineStr">
         <is>
           <t>USD</t>
@@ -27955,7 +29015,11 @@
           <t>76.299.358-9</t>
         </is>
       </c>
-      <c r="K451" t="inlineStr"/>
+      <c r="K451" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L451" t="inlineStr">
         <is>
           <t>USD</t>
@@ -28016,7 +29080,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K452" t="inlineStr"/>
+      <c r="K452" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L452" t="inlineStr">
         <is>
           <t>USD</t>
@@ -28077,7 +29145,11 @@
           <t>76.540.457-6</t>
         </is>
       </c>
-      <c r="K453" t="inlineStr"/>
+      <c r="K453" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L453" t="inlineStr">
         <is>
           <t>USD</t>
@@ -28321,7 +29393,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K457" t="inlineStr"/>
+      <c r="K457" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L457" t="inlineStr">
         <is>
           <t>USD</t>
@@ -28504,7 +29580,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K460" t="inlineStr"/>
+      <c r="K460" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L460" t="inlineStr">
         <is>
           <t>USD</t>
@@ -28626,7 +29706,11 @@
           <t>77.012.870-6</t>
         </is>
       </c>
-      <c r="K462" t="inlineStr"/>
+      <c r="K462" t="inlineStr">
+        <is>
+          <t>Coquimbo</t>
+        </is>
+      </c>
       <c r="L462" t="inlineStr">
         <is>
           <t>USD</t>
@@ -28687,7 +29771,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K463" t="inlineStr"/>
+      <c r="K463" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L463" t="inlineStr">
         <is>
           <t>USD</t>
@@ -28748,7 +29836,11 @@
           <t>76.556.184-1</t>
         </is>
       </c>
-      <c r="K464" t="inlineStr"/>
+      <c r="K464" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L464" t="inlineStr">
         <is>
           <t>USD</t>
@@ -28809,7 +29901,11 @@
           <t>76.540.457-6</t>
         </is>
       </c>
-      <c r="K465" t="inlineStr"/>
+      <c r="K465" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L465" t="inlineStr">
         <is>
           <t>USD</t>
@@ -28870,7 +29966,11 @@
           <t>78.906.980-8</t>
         </is>
       </c>
-      <c r="K466" t="inlineStr"/>
+      <c r="K466" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L466" t="inlineStr">
         <is>
           <t>USD</t>
@@ -29114,7 +30214,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K470" t="inlineStr"/>
+      <c r="K470" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L470" t="inlineStr">
         <is>
           <t>USD</t>
@@ -29175,7 +30279,11 @@
           <t>76.299.358-9</t>
         </is>
       </c>
-      <c r="K471" t="inlineStr"/>
+      <c r="K471" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L471" t="inlineStr">
         <is>
           <t>USD</t>
@@ -29358,7 +30466,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K474" t="inlineStr"/>
+      <c r="K474" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L474" t="inlineStr">
         <is>
           <t>USD</t>
@@ -29480,7 +30592,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K476" t="inlineStr"/>
+      <c r="K476" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L476" t="inlineStr">
         <is>
           <t>USD</t>
@@ -29541,7 +30657,11 @@
           <t>78.307.990-9</t>
         </is>
       </c>
-      <c r="K477" t="inlineStr"/>
+      <c r="K477" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L477" t="inlineStr">
         <is>
           <t>USD</t>
@@ -29602,7 +30722,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K478" t="inlineStr"/>
+      <c r="K478" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L478" t="inlineStr">
         <is>
           <t>USD</t>
@@ -29663,7 +30787,11 @@
           <t>77.012.870-6</t>
         </is>
       </c>
-      <c r="K479" t="inlineStr"/>
+      <c r="K479" t="inlineStr">
+        <is>
+          <t>Coquimbo</t>
+        </is>
+      </c>
       <c r="L479" t="inlineStr">
         <is>
           <t>USD</t>
@@ -29724,7 +30852,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K480" t="inlineStr"/>
+      <c r="K480" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L480" t="inlineStr">
         <is>
           <t>USD</t>
@@ -29785,7 +30917,11 @@
           <t>77.012.870-6</t>
         </is>
       </c>
-      <c r="K481" t="inlineStr"/>
+      <c r="K481" t="inlineStr">
+        <is>
+          <t>Coquimbo</t>
+        </is>
+      </c>
       <c r="L481" t="inlineStr">
         <is>
           <t>USD</t>
@@ -29846,7 +30982,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K482" t="inlineStr"/>
+      <c r="K482" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L482" t="inlineStr">
         <is>
           <t>USD</t>
@@ -29907,7 +31047,11 @@
           <t>78.307.990-9</t>
         </is>
       </c>
-      <c r="K483" t="inlineStr"/>
+      <c r="K483" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L483" t="inlineStr">
         <is>
           <t>USD</t>
@@ -29968,7 +31112,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K484" t="inlineStr"/>
+      <c r="K484" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L484" t="inlineStr">
         <is>
           <t>USD</t>
@@ -30090,7 +31238,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K486" t="inlineStr"/>
+      <c r="K486" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L486" t="inlineStr">
         <is>
           <t>USD</t>
@@ -30151,7 +31303,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K487" t="inlineStr"/>
+      <c r="K487" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L487" t="inlineStr">
         <is>
           <t>USD</t>
@@ -30212,7 +31368,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K488" t="inlineStr"/>
+      <c r="K488" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L488" t="inlineStr">
         <is>
           <t>USD</t>
@@ -30273,7 +31433,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K489" t="inlineStr"/>
+      <c r="K489" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L489" t="inlineStr">
         <is>
           <t>USD</t>
@@ -30578,7 +31742,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K494" t="inlineStr"/>
+      <c r="K494" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L494" t="inlineStr">
         <is>
           <t>USD</t>
@@ -30639,7 +31807,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K495" t="inlineStr"/>
+      <c r="K495" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L495" t="inlineStr">
         <is>
           <t>USD</t>
@@ -30700,7 +31872,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K496" t="inlineStr"/>
+      <c r="K496" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L496" t="inlineStr">
         <is>
           <t>USD</t>
@@ -30822,7 +31998,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K498" t="inlineStr"/>
+      <c r="K498" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L498" t="inlineStr">
         <is>
           <t>USD</t>
@@ -30883,7 +32063,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K499" t="inlineStr"/>
+      <c r="K499" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L499" t="inlineStr">
         <is>
           <t>USD</t>
@@ -30944,7 +32128,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K500" t="inlineStr"/>
+      <c r="K500" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L500" t="inlineStr">
         <is>
           <t>USD</t>
@@ -31066,7 +32254,11 @@
           <t>76.540.457-6</t>
         </is>
       </c>
-      <c r="K502" t="inlineStr"/>
+      <c r="K502" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L502" t="inlineStr">
         <is>
           <t>USD</t>
@@ -31127,7 +32319,11 @@
           <t>76.202.065-3</t>
         </is>
       </c>
-      <c r="K503" t="inlineStr"/>
+      <c r="K503" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L503" t="inlineStr">
         <is>
           <t>USD</t>
@@ -31188,7 +32384,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K504" t="inlineStr"/>
+      <c r="K504" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L504" t="inlineStr">
         <is>
           <t>USD</t>
@@ -31249,7 +32449,11 @@
           <t>78.906.980-8</t>
         </is>
       </c>
-      <c r="K505" t="inlineStr"/>
+      <c r="K505" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L505" t="inlineStr">
         <is>
           <t>USD</t>
@@ -31371,7 +32575,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K507" t="inlineStr"/>
+      <c r="K507" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L507" t="inlineStr">
         <is>
           <t>USD</t>
@@ -31432,7 +32640,11 @@
           <t>76.817.360-5</t>
         </is>
       </c>
-      <c r="K508" t="inlineStr"/>
+      <c r="K508" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L508" t="inlineStr">
         <is>
           <t>USD</t>
@@ -31554,7 +32766,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K510" t="inlineStr"/>
+      <c r="K510" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L510" t="inlineStr">
         <is>
           <t>USD</t>
@@ -31615,7 +32831,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K511" t="inlineStr"/>
+      <c r="K511" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L511" t="inlineStr">
         <is>
           <t>USD</t>
@@ -32042,7 +33262,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K518" t="inlineStr"/>
+      <c r="K518" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L518" t="inlineStr">
         <is>
           <t>USD</t>
@@ -32103,7 +33327,11 @@
           <t>76.213.681-3</t>
         </is>
       </c>
-      <c r="K519" t="inlineStr"/>
+      <c r="K519" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L519" t="inlineStr">
         <is>
           <t>USD</t>
@@ -32290,7 +33518,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K522" t="inlineStr"/>
+      <c r="K522" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L522" t="inlineStr">
         <is>
           <t>USD</t>
@@ -32351,7 +33583,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K523" t="inlineStr"/>
+      <c r="K523" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L523" t="inlineStr">
         <is>
           <t>USD</t>
@@ -32473,7 +33709,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K525" t="inlineStr"/>
+      <c r="K525" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L525" t="inlineStr">
         <is>
           <t>USD</t>
@@ -32778,7 +34018,11 @@
           <t>76.540.457-6</t>
         </is>
       </c>
-      <c r="K530" t="inlineStr"/>
+      <c r="K530" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L530" t="inlineStr">
         <is>
           <t>USD</t>
@@ -32839,7 +34083,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K531" t="inlineStr"/>
+      <c r="K531" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L531" t="inlineStr">
         <is>
           <t>USD</t>
@@ -32900,7 +34148,11 @@
           <t>76.202.065-3</t>
         </is>
       </c>
-      <c r="K532" t="inlineStr"/>
+      <c r="K532" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L532" t="inlineStr">
         <is>
           <t>USD</t>
@@ -33022,7 +34274,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K534" t="inlineStr"/>
+      <c r="K534" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L534" t="inlineStr">
         <is>
           <t>USD</t>
@@ -33083,7 +34339,11 @@
           <t>77.610.393-4</t>
         </is>
       </c>
-      <c r="K535" t="inlineStr"/>
+      <c r="K535" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L535" t="inlineStr">
         <is>
           <t>USD</t>
@@ -33205,7 +34465,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K537" t="inlineStr"/>
+      <c r="K537" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L537" t="inlineStr">
         <is>
           <t>USD</t>
@@ -33327,7 +34591,11 @@
           <t>77.012.870-6</t>
         </is>
       </c>
-      <c r="K539" t="inlineStr"/>
+      <c r="K539" t="inlineStr">
+        <is>
+          <t>Coquimbo</t>
+        </is>
+      </c>
       <c r="L539" t="inlineStr">
         <is>
           <t>USD</t>
@@ -33449,7 +34717,11 @@
           <t>77.012.870-6</t>
         </is>
       </c>
-      <c r="K541" t="inlineStr"/>
+      <c r="K541" t="inlineStr">
+        <is>
+          <t>Coquimbo</t>
+        </is>
+      </c>
       <c r="L541" t="inlineStr">
         <is>
           <t>USD</t>
@@ -33632,7 +34904,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K544" t="inlineStr"/>
+      <c r="K544" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L544" t="inlineStr">
         <is>
           <t>USD</t>
@@ -33693,7 +34969,11 @@
           <t>8.306.984-8</t>
         </is>
       </c>
-      <c r="K545" t="inlineStr"/>
+      <c r="K545" t="inlineStr">
+        <is>
+          <t>Atacama</t>
+        </is>
+      </c>
       <c r="L545" t="inlineStr">
         <is>
           <t>USD</t>
@@ -33815,7 +35095,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K547" t="inlineStr"/>
+      <c r="K547" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L547" t="inlineStr">
         <is>
           <t>USD</t>
@@ -33876,7 +35160,11 @@
           <t>76.540.457-6</t>
         </is>
       </c>
-      <c r="K548" t="inlineStr"/>
+      <c r="K548" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L548" t="inlineStr">
         <is>
           <t>USD</t>
@@ -33937,7 +35225,11 @@
           <t>89.842.300-k</t>
         </is>
       </c>
-      <c r="K549" t="inlineStr"/>
+      <c r="K549" t="inlineStr">
+        <is>
+          <t>Biobío</t>
+        </is>
+      </c>
       <c r="L549" t="inlineStr">
         <is>
           <t>USD</t>
@@ -34120,7 +35412,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K552" t="inlineStr"/>
+      <c r="K552" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L552" t="inlineStr">
         <is>
           <t>USD</t>
@@ -34242,7 +35538,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K554" t="inlineStr"/>
+      <c r="K554" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L554" t="inlineStr">
         <is>
           <t>USD</t>
@@ -34303,7 +35603,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K555" t="inlineStr"/>
+      <c r="K555" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L555" t="inlineStr">
         <is>
           <t>USD</t>
@@ -34364,7 +35668,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K556" t="inlineStr"/>
+      <c r="K556" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L556" t="inlineStr">
         <is>
           <t>USD</t>
@@ -34608,7 +35916,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K560" t="inlineStr"/>
+      <c r="K560" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L560" t="inlineStr">
         <is>
           <t>USD</t>
@@ -34669,7 +35981,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K561" t="inlineStr"/>
+      <c r="K561" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L561" t="inlineStr">
         <is>
           <t>USD</t>
@@ -34730,7 +36046,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K562" t="inlineStr"/>
+      <c r="K562" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L562" t="inlineStr">
         <is>
           <t>USD</t>
@@ -34791,7 +36111,11 @@
           <t>77.012.870-6</t>
         </is>
       </c>
-      <c r="K563" t="inlineStr"/>
+      <c r="K563" t="inlineStr">
+        <is>
+          <t>Coquimbo</t>
+        </is>
+      </c>
       <c r="L563" t="inlineStr">
         <is>
           <t>USD</t>
@@ -34852,7 +36176,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K564" t="inlineStr"/>
+      <c r="K564" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L564" t="inlineStr">
         <is>
           <t>USD</t>
@@ -34913,7 +36241,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K565" t="inlineStr"/>
+      <c r="K565" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L565" t="inlineStr">
         <is>
           <t>USD</t>
@@ -34974,7 +36306,11 @@
           <t>76.540.457-6</t>
         </is>
       </c>
-      <c r="K566" t="inlineStr"/>
+      <c r="K566" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L566" t="inlineStr">
         <is>
           <t>USD</t>
@@ -35096,7 +36432,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K568" t="inlineStr"/>
+      <c r="K568" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L568" t="inlineStr">
         <is>
           <t>USD</t>
@@ -35157,7 +36497,11 @@
           <t>89.842.300-k</t>
         </is>
       </c>
-      <c r="K569" t="inlineStr"/>
+      <c r="K569" t="inlineStr">
+        <is>
+          <t>Biobío</t>
+        </is>
+      </c>
       <c r="L569" t="inlineStr">
         <is>
           <t>USD</t>
@@ -35218,7 +36562,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K570" t="inlineStr"/>
+      <c r="K570" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L570" t="inlineStr">
         <is>
           <t>USD</t>
@@ -35279,7 +36627,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K571" t="inlineStr"/>
+      <c r="K571" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L571" t="inlineStr">
         <is>
           <t>USD</t>
@@ -35401,7 +36753,11 @@
           <t>76.202.065-3</t>
         </is>
       </c>
-      <c r="K573" t="inlineStr"/>
+      <c r="K573" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L573" t="inlineStr">
         <is>
           <t>USD</t>
@@ -35462,7 +36818,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K574" t="inlineStr"/>
+      <c r="K574" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L574" t="inlineStr">
         <is>
           <t>USD</t>
@@ -35645,7 +37005,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K577" t="inlineStr"/>
+      <c r="K577" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L577" t="inlineStr">
         <is>
           <t>USD</t>
@@ -35767,7 +37131,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K579" t="inlineStr"/>
+      <c r="K579" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L579" t="inlineStr">
         <is>
           <t>USD</t>
@@ -35950,7 +37318,11 @@
           <t>76.148.628-4</t>
         </is>
       </c>
-      <c r="K582" t="inlineStr"/>
+      <c r="K582" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L582" t="inlineStr">
         <is>
           <t>USD</t>
@@ -36011,7 +37383,11 @@
           <t>79.722.860-5</t>
         </is>
       </c>
-      <c r="K583" t="inlineStr"/>
+      <c r="K583" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L583" t="inlineStr">
         <is>
           <t>USD</t>
@@ -36133,7 +37509,11 @@
           <t>76.100.933-8</t>
         </is>
       </c>
-      <c r="K585" t="inlineStr"/>
+      <c r="K585" t="inlineStr">
+        <is>
+          <t>Biobío</t>
+        </is>
+      </c>
       <c r="L585" t="inlineStr">
         <is>
           <t>USD</t>
@@ -36194,7 +37574,11 @@
           <t>78.906.980-8</t>
         </is>
       </c>
-      <c r="K586" t="inlineStr"/>
+      <c r="K586" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L586" t="inlineStr">
         <is>
           <t>USD</t>
@@ -36316,7 +37700,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K588" t="inlineStr"/>
+      <c r="K588" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L588" t="inlineStr">
         <is>
           <t>USD</t>
@@ -36377,7 +37765,11 @@
           <t>89.842.300-k</t>
         </is>
       </c>
-      <c r="K589" t="inlineStr"/>
+      <c r="K589" t="inlineStr">
+        <is>
+          <t>Biobío</t>
+        </is>
+      </c>
       <c r="L589" t="inlineStr">
         <is>
           <t>USD</t>
@@ -36438,7 +37830,11 @@
           <t>77.012.870-6</t>
         </is>
       </c>
-      <c r="K590" t="inlineStr"/>
+      <c r="K590" t="inlineStr">
+        <is>
+          <t>Coquimbo</t>
+        </is>
+      </c>
       <c r="L590" t="inlineStr">
         <is>
           <t>USD</t>
@@ -36499,7 +37895,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K591" t="inlineStr"/>
+      <c r="K591" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L591" t="inlineStr">
         <is>
           <t>USD</t>
@@ -36682,7 +38082,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K594" t="inlineStr"/>
+      <c r="K594" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L594" t="inlineStr">
         <is>
           <t>USD</t>
@@ -36865,7 +38269,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K597" t="inlineStr"/>
+      <c r="K597" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L597" t="inlineStr">
         <is>
           <t>USD</t>
@@ -36987,7 +38395,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K599" t="inlineStr"/>
+      <c r="K599" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L599" t="inlineStr">
         <is>
           <t>USD</t>
@@ -37109,7 +38521,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K601" t="inlineStr"/>
+      <c r="K601" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L601" t="inlineStr">
         <is>
           <t>USD</t>
@@ -37170,7 +38586,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K602" t="inlineStr"/>
+      <c r="K602" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L602" t="inlineStr">
         <is>
           <t>USD</t>
@@ -37292,7 +38712,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K604" t="inlineStr"/>
+      <c r="K604" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L604" t="inlineStr">
         <is>
           <t>USD</t>
@@ -37658,7 +39082,11 @@
           <t>89.842.300-k</t>
         </is>
       </c>
-      <c r="K610" t="inlineStr"/>
+      <c r="K610" t="inlineStr">
+        <is>
+          <t>Biobío</t>
+        </is>
+      </c>
       <c r="L610" t="inlineStr">
         <is>
           <t>USD</t>
@@ -37780,7 +39208,11 @@
           <t>78.906.980-8</t>
         </is>
       </c>
-      <c r="K612" t="inlineStr"/>
+      <c r="K612" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L612" t="inlineStr">
         <is>
           <t>USD</t>
@@ -37841,7 +39273,11 @@
           <t>76.556.184-1</t>
         </is>
       </c>
-      <c r="K613" t="inlineStr"/>
+      <c r="K613" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L613" t="inlineStr">
         <is>
           <t>USD</t>
@@ -37902,7 +39338,11 @@
           <t>76.299.358-9</t>
         </is>
       </c>
-      <c r="K614" t="inlineStr"/>
+      <c r="K614" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L614" t="inlineStr">
         <is>
           <t>USD</t>
@@ -37963,7 +39403,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K615" t="inlineStr"/>
+      <c r="K615" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L615" t="inlineStr">
         <is>
           <t>USD</t>
@@ -38024,7 +39468,11 @@
           <t>76.540.457-6</t>
         </is>
       </c>
-      <c r="K616" t="inlineStr"/>
+      <c r="K616" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L616" t="inlineStr">
         <is>
           <t>USD</t>
@@ -38085,7 +39533,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K617" t="inlineStr"/>
+      <c r="K617" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L617" t="inlineStr">
         <is>
           <t>USD</t>
@@ -38146,7 +39598,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K618" t="inlineStr"/>
+      <c r="K618" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L618" t="inlineStr">
         <is>
           <t>USD</t>
@@ -38268,7 +39724,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K620" t="inlineStr"/>
+      <c r="K620" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L620" t="inlineStr">
         <is>
           <t>USD</t>
@@ -38329,7 +39789,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K621" t="inlineStr"/>
+      <c r="K621" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L621" t="inlineStr">
         <is>
           <t>USD</t>
@@ -38390,7 +39854,11 @@
           <t>77.082.051-0</t>
         </is>
       </c>
-      <c r="K622" t="inlineStr"/>
+      <c r="K622" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L622" t="inlineStr">
         <is>
           <t>USD</t>
@@ -38451,7 +39919,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K623" t="inlineStr"/>
+      <c r="K623" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L623" t="inlineStr">
         <is>
           <t>USD</t>
@@ -38512,7 +39984,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K624" t="inlineStr"/>
+      <c r="K624" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L624" t="inlineStr">
         <is>
           <t>USD</t>
@@ -38573,7 +40049,11 @@
           <t>76.213.681-3</t>
         </is>
       </c>
-      <c r="K625" t="inlineStr"/>
+      <c r="K625" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L625" t="inlineStr">
         <is>
           <t>USD</t>
@@ -38695,7 +40175,11 @@
           <t>76.299.358-9</t>
         </is>
       </c>
-      <c r="K627" t="inlineStr"/>
+      <c r="K627" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L627" t="inlineStr">
         <is>
           <t>USD</t>
@@ -38817,7 +40301,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K629" t="inlineStr"/>
+      <c r="K629" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L629" t="inlineStr">
         <is>
           <t>USD</t>
@@ -38878,7 +40366,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K630" t="inlineStr"/>
+      <c r="K630" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L630" t="inlineStr">
         <is>
           <t>USD</t>
@@ -38939,7 +40431,11 @@
           <t>77.806.000-0</t>
         </is>
       </c>
-      <c r="K631" t="inlineStr"/>
+      <c r="K631" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L631" t="inlineStr">
         <is>
           <t>USD</t>
@@ -39000,7 +40496,11 @@
           <t>77.012.870-6</t>
         </is>
       </c>
-      <c r="K632" t="inlineStr"/>
+      <c r="K632" t="inlineStr">
+        <is>
+          <t>Coquimbo</t>
+        </is>
+      </c>
       <c r="L632" t="inlineStr">
         <is>
           <t>USD</t>
@@ -39122,7 +40622,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K634" t="inlineStr"/>
+      <c r="K634" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L634" t="inlineStr">
         <is>
           <t>USD</t>
@@ -39183,7 +40687,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K635" t="inlineStr"/>
+      <c r="K635" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L635" t="inlineStr">
         <is>
           <t>USD</t>
@@ -39244,7 +40752,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K636" t="inlineStr"/>
+      <c r="K636" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L636" t="inlineStr">
         <is>
           <t>USD</t>
@@ -39305,7 +40817,11 @@
           <t>78.906.980-8</t>
         </is>
       </c>
-      <c r="K637" t="inlineStr"/>
+      <c r="K637" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L637" t="inlineStr">
         <is>
           <t>USD</t>
@@ -39366,7 +40882,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K638" t="inlineStr"/>
+      <c r="K638" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L638" t="inlineStr">
         <is>
           <t>USD</t>
@@ -39427,7 +40947,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K639" t="inlineStr"/>
+      <c r="K639" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L639" t="inlineStr">
         <is>
           <t>USD</t>
@@ -39671,7 +41195,11 @@
           <t>76.540.457-6</t>
         </is>
       </c>
-      <c r="K643" t="inlineStr"/>
+      <c r="K643" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L643" t="inlineStr">
         <is>
           <t>USD</t>
@@ -39732,7 +41260,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K644" t="inlineStr"/>
+      <c r="K644" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L644" t="inlineStr">
         <is>
           <t>USD</t>
@@ -39793,7 +41325,11 @@
           <t>76.299.358-9</t>
         </is>
       </c>
-      <c r="K645" t="inlineStr"/>
+      <c r="K645" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L645" t="inlineStr">
         <is>
           <t>USD</t>
@@ -39915,7 +41451,11 @@
           <t>77.610.393-4</t>
         </is>
       </c>
-      <c r="K647" t="inlineStr"/>
+      <c r="K647" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L647" t="inlineStr">
         <is>
           <t>USD</t>
@@ -40037,7 +41577,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K649" t="inlineStr"/>
+      <c r="K649" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L649" t="inlineStr">
         <is>
           <t>USD</t>
@@ -40281,7 +41825,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K653" t="inlineStr"/>
+      <c r="K653" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L653" t="inlineStr">
         <is>
           <t>USD</t>
@@ -40525,7 +42073,11 @@
           <t>76.100.933-8</t>
         </is>
       </c>
-      <c r="K657" t="inlineStr"/>
+      <c r="K657" t="inlineStr">
+        <is>
+          <t>Biobío</t>
+        </is>
+      </c>
       <c r="L657" t="inlineStr">
         <is>
           <t>USD</t>
@@ -40586,7 +42138,11 @@
           <t>76.540.457-6</t>
         </is>
       </c>
-      <c r="K658" t="inlineStr"/>
+      <c r="K658" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L658" t="inlineStr">
         <is>
           <t>USD</t>
@@ -40708,7 +42264,11 @@
           <t>76.202.065-3</t>
         </is>
       </c>
-      <c r="K660" t="inlineStr"/>
+      <c r="K660" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L660" t="inlineStr">
         <is>
           <t>USD</t>
@@ -40769,7 +42329,11 @@
           <t>76.299.358-9</t>
         </is>
       </c>
-      <c r="K661" t="inlineStr"/>
+      <c r="K661" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L661" t="inlineStr">
         <is>
           <t>USD</t>
@@ -40830,7 +42394,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K662" t="inlineStr"/>
+      <c r="K662" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L662" t="inlineStr">
         <is>
           <t>USD</t>
@@ -40891,7 +42459,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K663" t="inlineStr"/>
+      <c r="K663" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L663" t="inlineStr">
         <is>
           <t>USD</t>
@@ -40952,7 +42524,11 @@
           <t>77.012.870-6</t>
         </is>
       </c>
-      <c r="K664" t="inlineStr"/>
+      <c r="K664" t="inlineStr">
+        <is>
+          <t>Coquimbo</t>
+        </is>
+      </c>
       <c r="L664" t="inlineStr">
         <is>
           <t>USD</t>
@@ -41013,7 +42589,11 @@
           <t>79.722.860-5</t>
         </is>
       </c>
-      <c r="K665" t="inlineStr"/>
+      <c r="K665" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L665" t="inlineStr">
         <is>
           <t>USD</t>
@@ -41074,7 +42654,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K666" t="inlineStr"/>
+      <c r="K666" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L666" t="inlineStr">
         <is>
           <t>USD</t>
@@ -41196,7 +42780,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K668" t="inlineStr"/>
+      <c r="K668" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L668" t="inlineStr">
         <is>
           <t>USD</t>
@@ -41318,7 +42906,11 @@
           <t>76.202.065-3</t>
         </is>
       </c>
-      <c r="K670" t="inlineStr"/>
+      <c r="K670" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L670" t="inlineStr">
         <is>
           <t>USD</t>
@@ -41501,7 +43093,11 @@
           <t>77.012.870-6</t>
         </is>
       </c>
-      <c r="K673" t="inlineStr"/>
+      <c r="K673" t="inlineStr">
+        <is>
+          <t>Coquimbo</t>
+        </is>
+      </c>
       <c r="L673" t="inlineStr">
         <is>
           <t>USD</t>
@@ -41623,7 +43219,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K675" t="inlineStr"/>
+      <c r="K675" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L675" t="inlineStr">
         <is>
           <t>USD</t>
@@ -41806,7 +43406,11 @@
           <t>77.610.393-4</t>
         </is>
       </c>
-      <c r="K678" t="inlineStr"/>
+      <c r="K678" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L678" t="inlineStr">
         <is>
           <t>USD</t>
@@ -41928,7 +43532,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K680" t="inlineStr"/>
+      <c r="K680" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L680" t="inlineStr">
         <is>
           <t>USD</t>
@@ -42050,7 +43658,11 @@
           <t>78.906.980-8</t>
         </is>
       </c>
-      <c r="K682" t="inlineStr"/>
+      <c r="K682" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L682" t="inlineStr">
         <is>
           <t>USD</t>
@@ -42233,7 +43845,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K685" t="inlineStr"/>
+      <c r="K685" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L685" t="inlineStr">
         <is>
           <t>USD</t>
@@ -42294,7 +43910,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K686" t="inlineStr"/>
+      <c r="K686" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L686" t="inlineStr">
         <is>
           <t>USD</t>
@@ -42416,7 +44036,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K688" t="inlineStr"/>
+      <c r="K688" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L688" t="inlineStr">
         <is>
           <t>USD</t>
@@ -42477,7 +44101,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K689" t="inlineStr"/>
+      <c r="K689" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L689" t="inlineStr">
         <is>
           <t>USD</t>
@@ -42538,7 +44166,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K690" t="inlineStr"/>
+      <c r="K690" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L690" t="inlineStr">
         <is>
           <t>USD</t>
@@ -42599,7 +44231,11 @@
           <t>89.842.300-k</t>
         </is>
       </c>
-      <c r="K691" t="inlineStr"/>
+      <c r="K691" t="inlineStr">
+        <is>
+          <t>Biobío</t>
+        </is>
+      </c>
       <c r="L691" t="inlineStr">
         <is>
           <t>USD</t>
@@ -42721,7 +44357,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K693" t="inlineStr"/>
+      <c r="K693" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L693" t="inlineStr">
         <is>
           <t>USD</t>
@@ -42782,7 +44422,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K694" t="inlineStr"/>
+      <c r="K694" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L694" t="inlineStr">
         <is>
           <t>USD</t>
@@ -42843,7 +44487,11 @@
           <t>77.012.870-6</t>
         </is>
       </c>
-      <c r="K695" t="inlineStr"/>
+      <c r="K695" t="inlineStr">
+        <is>
+          <t>Coquimbo</t>
+        </is>
+      </c>
       <c r="L695" t="inlineStr">
         <is>
           <t>USD</t>

--- a/docs/oc-mensuales/articulos-de-aseo-e-higiene/jun-2025.xlsx
+++ b/docs/oc-mensuales/articulos-de-aseo-e-higiene/jun-2025.xlsx
@@ -822,7 +822,11 @@
           <t>76.287.853-4</t>
         </is>
       </c>
-      <c r="K6" t="inlineStr"/>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L6" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1013,7 +1017,11 @@
           <t>76.287.853-4</t>
         </is>
       </c>
-      <c r="K9" t="inlineStr"/>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L9" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1074,7 +1082,11 @@
           <t>76.287.853-4</t>
         </is>
       </c>
-      <c r="K10" t="inlineStr"/>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L10" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1322,7 +1334,11 @@
           <t>76.287.853-4</t>
         </is>
       </c>
-      <c r="K14" t="inlineStr"/>
+      <c r="K14" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L14" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1891,7 +1907,11 @@
           <t>76.287.853-4</t>
         </is>
       </c>
-      <c r="K23" t="inlineStr"/>
+      <c r="K23" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L23" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1952,7 +1972,11 @@
           <t>76.287.853-4</t>
         </is>
       </c>
-      <c r="K24" t="inlineStr"/>
+      <c r="K24" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L24" t="inlineStr">
         <is>
           <t>USD</t>
@@ -3598,7 +3622,11 @@
           <t>76.287.853-4</t>
         </is>
       </c>
-      <c r="K50" t="inlineStr"/>
+      <c r="K50" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L50" t="inlineStr">
         <is>
           <t>USD</t>
@@ -4874,7 +4902,11 @@
           <t>76.287.853-4</t>
         </is>
       </c>
-      <c r="K70" t="inlineStr"/>
+      <c r="K70" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L70" t="inlineStr">
         <is>
           <t>USD</t>
@@ -5126,7 +5158,11 @@
           <t>76.287.853-4</t>
         </is>
       </c>
-      <c r="K74" t="inlineStr"/>
+      <c r="K74" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L74" t="inlineStr">
         <is>
           <t>USD</t>
@@ -5504,7 +5540,11 @@
           <t>76.287.853-4</t>
         </is>
       </c>
-      <c r="K80" t="inlineStr"/>
+      <c r="K80" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L80" t="inlineStr">
         <is>
           <t>USD</t>
@@ -5691,7 +5731,11 @@
           <t>76.287.853-4</t>
         </is>
       </c>
-      <c r="K83" t="inlineStr"/>
+      <c r="K83" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L83" t="inlineStr">
         <is>
           <t>USD</t>
@@ -6195,7 +6239,11 @@
           <t>76.287.853-4</t>
         </is>
       </c>
-      <c r="K91" t="inlineStr"/>
+      <c r="K91" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L91" t="inlineStr">
         <is>
           <t>USD</t>
@@ -7284,7 +7332,11 @@
           <t>76.287.853-4</t>
         </is>
       </c>
-      <c r="K108" t="inlineStr"/>
+      <c r="K108" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L108" t="inlineStr">
         <is>
           <t>USD</t>
@@ -7658,7 +7710,11 @@
           <t>76.287.853-4</t>
         </is>
       </c>
-      <c r="K114" t="inlineStr"/>
+      <c r="K114" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L114" t="inlineStr">
         <is>
           <t>USD</t>
@@ -8162,7 +8218,11 @@
           <t>76.287.853-4</t>
         </is>
       </c>
-      <c r="K122" t="inlineStr"/>
+      <c r="K122" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L122" t="inlineStr">
         <is>
           <t>USD</t>
@@ -9365,7 +9425,11 @@
           <t>76.287.853-4</t>
         </is>
       </c>
-      <c r="K141" t="inlineStr"/>
+      <c r="K141" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L141" t="inlineStr">
         <is>
           <t>USD</t>
@@ -10828,7 +10892,11 @@
           <t>76.287.853-4</t>
         </is>
       </c>
-      <c r="K164" t="inlineStr"/>
+      <c r="K164" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L164" t="inlineStr">
         <is>
           <t>USD</t>
@@ -11259,7 +11327,11 @@
           <t>76.287.853-4</t>
         </is>
       </c>
-      <c r="K171" t="inlineStr"/>
+      <c r="K171" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L171" t="inlineStr">
         <is>
           <t>USD</t>
@@ -11511,7 +11583,11 @@
           <t>76.287.853-4</t>
         </is>
       </c>
-      <c r="K175" t="inlineStr"/>
+      <c r="K175" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L175" t="inlineStr">
         <is>
           <t>USD</t>
@@ -13295,7 +13371,11 @@
           <t>76.287.853-4</t>
         </is>
       </c>
-      <c r="K203" t="inlineStr"/>
+      <c r="K203" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L203" t="inlineStr">
         <is>
           <t>USD</t>
@@ -13994,7 +14074,11 @@
           <t>76.287.853-4</t>
         </is>
       </c>
-      <c r="K214" t="inlineStr"/>
+      <c r="K214" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L214" t="inlineStr">
         <is>
           <t>USD</t>
@@ -15339,7 +15423,11 @@
           <t>76.287.853-4</t>
         </is>
       </c>
-      <c r="K235" t="inlineStr"/>
+      <c r="K235" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L235" t="inlineStr">
         <is>
           <t>USD</t>
@@ -16103,7 +16191,11 @@
           <t>76.287.853-4</t>
         </is>
       </c>
-      <c r="K247" t="inlineStr"/>
+      <c r="K247" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L247" t="inlineStr">
         <is>
           <t>USD</t>
@@ -16871,7 +16963,11 @@
           <t>76.287.853-4</t>
         </is>
       </c>
-      <c r="K259" t="inlineStr"/>
+      <c r="K259" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L259" t="inlineStr">
         <is>
           <t>USD</t>
@@ -17436,7 +17532,11 @@
           <t>76.287.853-4</t>
         </is>
       </c>
-      <c r="K268" t="inlineStr"/>
+      <c r="K268" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L268" t="inlineStr">
         <is>
           <t>USD</t>
@@ -18200,7 +18300,11 @@
           <t>76.287.853-4</t>
         </is>
       </c>
-      <c r="K280" t="inlineStr"/>
+      <c r="K280" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L280" t="inlineStr">
         <is>
           <t>USD</t>
@@ -18456,7 +18560,11 @@
           <t>76.287.853-4</t>
         </is>
       </c>
-      <c r="K284" t="inlineStr"/>
+      <c r="K284" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L284" t="inlineStr">
         <is>
           <t>USD</t>
@@ -19289,7 +19397,11 @@
           <t>76.287.853-4</t>
         </is>
       </c>
-      <c r="K297" t="inlineStr"/>
+      <c r="K297" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L297" t="inlineStr">
         <is>
           <t>USD</t>
@@ -19996,7 +20108,11 @@
           <t>76.287.853-4</t>
         </is>
       </c>
-      <c r="K308" t="inlineStr"/>
+      <c r="K308" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L308" t="inlineStr">
         <is>
           <t>USD</t>
@@ -20187,7 +20303,11 @@
           <t>76.287.853-4</t>
         </is>
       </c>
-      <c r="K311" t="inlineStr"/>
+      <c r="K311" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L311" t="inlineStr">
         <is>
           <t>USD</t>
@@ -23670,7 +23790,11 @@
           <t>76.287.853-4</t>
         </is>
       </c>
-      <c r="K366" t="inlineStr"/>
+      <c r="K366" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L366" t="inlineStr">
         <is>
           <t>USD</t>
@@ -23731,7 +23855,11 @@
           <t>76.287.853-4</t>
         </is>
       </c>
-      <c r="K367" t="inlineStr"/>
+      <c r="K367" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L367" t="inlineStr">
         <is>
           <t>USD</t>
@@ -24174,7 +24302,11 @@
           <t>76.287.853-4</t>
         </is>
       </c>
-      <c r="K374" t="inlineStr"/>
+      <c r="K374" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L374" t="inlineStr">
         <is>
           <t>USD</t>
@@ -24361,7 +24493,11 @@
           <t>76.287.853-4</t>
         </is>
       </c>
-      <c r="K377" t="inlineStr"/>
+      <c r="K377" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L377" t="inlineStr">
         <is>
           <t>USD</t>
@@ -25182,7 +25318,11 @@
           <t>76.287.853-4</t>
         </is>
       </c>
-      <c r="K390" t="inlineStr"/>
+      <c r="K390" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L390" t="inlineStr">
         <is>
           <t>USD</t>
@@ -25678,7 +25818,11 @@
           <t>76.287.853-4</t>
         </is>
       </c>
-      <c r="K398" t="inlineStr"/>
+      <c r="K398" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L398" t="inlineStr">
         <is>
           <t>USD</t>
@@ -26304,7 +26448,11 @@
           <t>76.287.853-4</t>
         </is>
       </c>
-      <c r="K408" t="inlineStr"/>
+      <c r="K408" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L408" t="inlineStr">
         <is>
           <t>USD</t>
@@ -26430,7 +26578,11 @@
           <t>76.287.853-4</t>
         </is>
       </c>
-      <c r="K410" t="inlineStr"/>
+      <c r="K410" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L410" t="inlineStr">
         <is>
           <t>USD</t>
@@ -26808,7 +26960,11 @@
           <t>76.287.853-4</t>
         </is>
       </c>
-      <c r="K416" t="inlineStr"/>
+      <c r="K416" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L416" t="inlineStr">
         <is>
           <t>USD</t>
@@ -26869,7 +27025,11 @@
           <t>76.287.853-4</t>
         </is>
       </c>
-      <c r="K417" t="inlineStr"/>
+      <c r="K417" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L417" t="inlineStr">
         <is>
           <t>USD</t>
@@ -27434,7 +27594,11 @@
           <t>76.287.853-4</t>
         </is>
       </c>
-      <c r="K426" t="inlineStr"/>
+      <c r="K426" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L426" t="inlineStr">
         <is>
           <t>USD</t>
@@ -28706,7 +28870,11 @@
           <t>76.287.853-4</t>
         </is>
       </c>
-      <c r="K446" t="inlineStr"/>
+      <c r="K446" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L446" t="inlineStr">
         <is>
           <t>USD</t>
@@ -28828,7 +28996,11 @@
           <t>76.287.853-4</t>
         </is>
       </c>
-      <c r="K448" t="inlineStr"/>
+      <c r="K448" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L448" t="inlineStr">
         <is>
           <t>USD</t>
@@ -29271,7 +29443,11 @@
           <t>76.287.853-4</t>
         </is>
       </c>
-      <c r="K455" t="inlineStr"/>
+      <c r="K455" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L455" t="inlineStr">
         <is>
           <t>USD</t>
@@ -29519,7 +29695,11 @@
           <t>76.287.853-4</t>
         </is>
       </c>
-      <c r="K459" t="inlineStr"/>
+      <c r="K459" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L459" t="inlineStr">
         <is>
           <t>USD</t>
@@ -31177,7 +31357,11 @@
           <t>76.287.853-4</t>
         </is>
       </c>
-      <c r="K485" t="inlineStr"/>
+      <c r="K485" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L485" t="inlineStr">
         <is>
           <t>USD</t>
@@ -32193,7 +32377,11 @@
           <t>76.287.853-4</t>
         </is>
       </c>
-      <c r="K501" t="inlineStr"/>
+      <c r="K501" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L501" t="inlineStr">
         <is>
           <t>USD</t>
@@ -32896,7 +33084,11 @@
           <t>76.287.853-4</t>
         </is>
       </c>
-      <c r="K512" t="inlineStr"/>
+      <c r="K512" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L512" t="inlineStr">
         <is>
           <t>USD</t>
@@ -32957,7 +33149,11 @@
           <t>76.287.853-4</t>
         </is>
       </c>
-      <c r="K513" t="inlineStr"/>
+      <c r="K513" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L513" t="inlineStr">
         <is>
           <t>USD</t>
@@ -34213,7 +34409,11 @@
           <t>76.287.853-4</t>
         </is>
       </c>
-      <c r="K533" t="inlineStr"/>
+      <c r="K533" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L533" t="inlineStr">
         <is>
           <t>USD</t>
@@ -34404,7 +34604,11 @@
           <t>76.287.853-4</t>
         </is>
       </c>
-      <c r="K536" t="inlineStr"/>
+      <c r="K536" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L536" t="inlineStr">
         <is>
           <t>USD</t>
@@ -34530,7 +34734,11 @@
           <t>76.287.853-4</t>
         </is>
       </c>
-      <c r="K538" t="inlineStr"/>
+      <c r="K538" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L538" t="inlineStr">
         <is>
           <t>USD</t>
@@ -34656,7 +34864,11 @@
           <t>76.287.853-4</t>
         </is>
       </c>
-      <c r="K540" t="inlineStr"/>
+      <c r="K540" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L540" t="inlineStr">
         <is>
           <t>USD</t>
@@ -35855,7 +36067,11 @@
           <t>76.287.853-4</t>
         </is>
       </c>
-      <c r="K559" t="inlineStr"/>
+      <c r="K559" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L559" t="inlineStr">
         <is>
           <t>USD</t>
@@ -36883,7 +37099,11 @@
           <t>76.287.853-4</t>
         </is>
       </c>
-      <c r="K575" t="inlineStr"/>
+      <c r="K575" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L575" t="inlineStr">
         <is>
           <t>USD</t>
@@ -36944,7 +37164,11 @@
           <t>76.287.853-4</t>
         </is>
       </c>
-      <c r="K576" t="inlineStr"/>
+      <c r="K576" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L576" t="inlineStr">
         <is>
           <t>USD</t>
@@ -38147,7 +38371,11 @@
           <t>76.287.853-4</t>
         </is>
       </c>
-      <c r="K595" t="inlineStr"/>
+      <c r="K595" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L595" t="inlineStr">
         <is>
           <t>USD</t>
@@ -39663,7 +39891,11 @@
           <t>76.287.853-4</t>
         </is>
       </c>
-      <c r="K619" t="inlineStr"/>
+      <c r="K619" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L619" t="inlineStr">
         <is>
           <t>USD</t>
@@ -40561,7 +40793,11 @@
           <t>76.287.853-4</t>
         </is>
       </c>
-      <c r="K633" t="inlineStr"/>
+      <c r="K633" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L633" t="inlineStr">
         <is>
           <t>USD</t>
@@ -41390,7 +41626,11 @@
           <t>76.287.853-4</t>
         </is>
       </c>
-      <c r="K646" t="inlineStr"/>
+      <c r="K646" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L646" t="inlineStr">
         <is>
           <t>USD</t>
@@ -41516,7 +41756,11 @@
           <t>76.287.853-4</t>
         </is>
       </c>
-      <c r="K648" t="inlineStr"/>
+      <c r="K648" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L648" t="inlineStr">
         <is>
           <t>USD</t>
@@ -41764,7 +42008,11 @@
           <t>76.287.853-4</t>
         </is>
       </c>
-      <c r="K652" t="inlineStr"/>
+      <c r="K652" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L652" t="inlineStr">
         <is>
           <t>USD</t>
@@ -41951,7 +42199,11 @@
           <t>76.287.853-4</t>
         </is>
       </c>
-      <c r="K655" t="inlineStr"/>
+      <c r="K655" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L655" t="inlineStr">
         <is>
           <t>USD</t>
@@ -42719,7 +42971,11 @@
           <t>76.287.853-4</t>
         </is>
       </c>
-      <c r="K667" t="inlineStr"/>
+      <c r="K667" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L667" t="inlineStr">
         <is>
           <t>USD</t>
@@ -42845,7 +43101,11 @@
           <t>76.287.853-4</t>
         </is>
       </c>
-      <c r="K669" t="inlineStr"/>
+      <c r="K669" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L669" t="inlineStr">
         <is>
           <t>USD</t>
@@ -42971,7 +43231,11 @@
           <t>76.287.853-4</t>
         </is>
       </c>
-      <c r="K671" t="inlineStr"/>
+      <c r="K671" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L671" t="inlineStr">
         <is>
           <t>USD</t>
@@ -43032,7 +43296,11 @@
           <t>76.287.853-4</t>
         </is>
       </c>
-      <c r="K672" t="inlineStr"/>
+      <c r="K672" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L672" t="inlineStr">
         <is>
           <t>USD</t>
@@ -43471,7 +43739,11 @@
           <t>76.287.853-4</t>
         </is>
       </c>
-      <c r="K679" t="inlineStr"/>
+      <c r="K679" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L679" t="inlineStr">
         <is>
           <t>USD</t>
@@ -43723,7 +43995,11 @@
           <t>76.287.853-4</t>
         </is>
       </c>
-      <c r="K683" t="inlineStr"/>
+      <c r="K683" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L683" t="inlineStr">
         <is>
           <t>USD</t>
@@ -43975,7 +44251,11 @@
           <t>76.287.853-4</t>
         </is>
       </c>
-      <c r="K687" t="inlineStr"/>
+      <c r="K687" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L687" t="inlineStr">
         <is>
           <t>USD</t>
